--- a/leads_odontologia_curitiba.xlsx
+++ b/leads_odontologia_curitiba.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google Meu Negcio para Odontologia</t>
+          <t>OralClick Odontologia Curitiba 4.9 (4) Clnico</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Google Meu Negócio para Odontologia em Curitiba | AUDITSEO</t>
+          <t xml:space="preserve">OralClick Odontologia Curitiba · 4.9 (4) · Clínico Geral em... | </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Em odontologia, o perfil local precisa sustentar proximidade, clareza e ação rápida. em Curitiba. Co...</t>
+          <t>OralClick Odontologia Curitiba em Cajuru, Curitiba (PR) — Clínico Geral. Avaliação 4.9 no Google (4 ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,28 +521,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.auditseo.com.br/servicos/google-meu-negocio-para-odontologia-em-curitiba/</t>
+          <t>https://dentmap.com.br/dentistas/curitiba/oralclick-odontologia-curitiba-bdb06076</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41 99572-0198</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>554199572019800</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Google%20Meu%20Negcio%20para%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/OralClick%20Odontologia%20Curitiba%204.9%20%284%29%20Clnico%20curitiba</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Google Meu Negcio para Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da OralClick Odontologia Curitiba 4.9 (4) Clnico aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -552,29 +548,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Google Meu Negcio para Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a OralClick Odontologia Curitiba 4.9 (4) Clnico?</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://wa.me/554199572019800?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Google%20Meu%20Negcio%20para%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OralClick%20Odontologia%20Curitiba%204.9%20%284%29%20Clnico%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://wa.me/554199572019800?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Google%20Meu%20Negcio%20para%20Odontologia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OralClick%20Odontologia%20Curitiba%204.9%20%284%29%20Clnico%3F</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yandex Maps: search for places, transport, an</t>
+          <t>CNPJ: 46.364.200/0001-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yandex Maps: search for places, transport, and routes</t>
+          <t>CNPJ: 46.364.200/0001-24 - Dental Design Curitiba Odontologia...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -589,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yandex Maps will help you find your destination even if you don't have the exact address — get a rou...</t>
+          <t>O CNPJ da empresa Dental Design Curitiba Odontologia Ltda (Dental Design Curitiba) é 46.364.200/0001...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -599,24 +595,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://yandex.com/maps/</t>
+          <t>https://www.nacionalconsultas.com.br/cnpj/dental-design-curitiba-odontologia-ltda-46364200000124</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(41) 9851-2345</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>554198512345</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20curitiba</t>
+          <t>https://www.google.com/maps/search/CNPJ%3A%2046.364.200/0001-24%20curitiba</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Yandex Maps: search for places, transport, an aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da CNPJ: 46.364.200/0001-24 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -626,29 +626,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Yandex Maps: search for places, transport, an?</t>
+Posso te mandar a prévia demonstrativa que fiz para a CNPJ: 46.364.200/0001-24?</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554198512345?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%3A%2046.364.200/0001-24%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Yandex%20Maps%3A%20search%20for%20places%2C%20transport%2C%20an%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554198512345?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%3A%2046.364.200/0001-24%3F</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atendimento Hospitalar</t>
+          <t>Odontologia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atendimento Hospitalar em Curitiba — Odontologia sob AG</t>
+          <t>Odontologia em Curitiba | Murano Odontologia (41) 3253-1907 ...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dentista família em Curitiba especializada em autismo (TEA), necessidades especiais, sedação conscie...</t>
+          <t>A Clínica Murano Odontologia de Referência dá bons motivos para você ter um sorriso bonito e saudáve...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -673,28 +673,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.ninaodontologia.com.br/atendimento-hospitalar</t>
+          <t>https://muranoodontologia.com.br/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(41) 3111-3000</t>
+          <t>(41) 3253-1907</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>55413111300000</t>
+          <t>554132531907</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Atendimento%20Hospitalar%20curitiba</t>
+          <t>https://www.google.com/maps/search/Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Atendimento Hospitalar aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -704,29 +704,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Atendimento Hospitalar?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odontologia?</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://wa.me/55413111300000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Atendimento%20Hospitalar%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554132531907?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://wa.me/55413111300000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Atendimento%20Hospitalar%3F</t>
+          <t>https://wa.me/554132531907?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OralClick Odontologia Curitiba 4.9 (4) Clnico</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">OralClick Odontologia Curitiba · 4.9 (4) · Clínico Geral em... | </t>
+          <t>Curitiba - Centro - PR - Mappi Odontologia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OralClick Odontologia Curitiba em Cajuru, Curitiba (PR) — Clínico Geral. Avaliação 4.9 no Google (4 ...</t>
+          <t>Conheça a unidade da Mappi no centro de Curitiba/PR e agende a sua avaliação agora mesmo para conqui...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -751,28 +751,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://dentmap.com.br/dentistas/curitiba/oralclick-odontologia-curitiba-bdb06076</t>
+          <t>https://mappiodontologia.com.br/curitiba-centro-pr/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>41 30860707</t>
+          <t>(41) 9876-2903</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55413086070700</t>
+          <t>554198762903</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/OralClick%20Odontologia%20Curitiba%204.9%20%284%29%20Clnico%20curitiba</t>
+          <t>https://www.google.com/maps/search/Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da OralClick Odontologia Curitiba 4.9 (4) Clnico aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -782,29 +782,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a OralClick Odontologia Curitiba 4.9 (4) Clnico?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Curitiba?</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://wa.me/55413086070700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OralClick%20Odontologia%20Curitiba%204.9%20%284%29%20Clnico%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554198762903?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://wa.me/55413086070700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OralClick%20Odontologia%20Curitiba%204.9%20%284%29%20Clnico%3F</t>
+          <t>https://wa.me/554198762903?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CNPJ: 28.274.955/0001-56</t>
+          <t>Encontrar seu smartphone</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CNPJ: 28.274.955/0001-56 - Oral Unic Odontologia Curitiba Ltda...</t>
+          <t>Encontrar seu smartphone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,34 +819,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>O CNPJ da empresa Oral Unic Odontologia Curitiba Ltda (Oral Unic) é 28.274.955/0001-56. Com sede em ...</t>
+          <t>Configurações da Conta do Google. Ajuda. Fazer login....</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.nacionalconsultas.com.br/cnpj/oral-unic-odontologia-curitiba-ltda-28274955000156</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/CNPJ%3A%2028.274.955/0001-56%20curitiba</t>
+          <t>https://www.google.com/maps/search/Encontrar%20seu%20smartphone%20curitiba</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da CNPJ: 28.274.955/0001-56 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Encontrar seu smartphone aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -856,29 +856,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a CNPJ: 28.274.955/0001-56?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Encontrar seu smartphone?</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=CNPJ%3A%2028.274.955/0001-56%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Encontrar%20seu%20smartphone%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=CNPJ%3A%2028.274.955/0001-56%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Encontrar%20seu%20smartphone%3F</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IGO</t>
+          <t>OpenGuessr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IGO - Instituto Guskuma de Odontologia - Curitiba... | Top-Rated.</t>
+          <t>OpenGuessr - Error</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Discover top rated places in Curitiba. IGO - Instituto Guskuma de Odontologia - Curitiba - Dental im...</t>
+          <t>Openguessr - guess the country based off Google maps....</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -903,28 +903,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.top-rated.online/cities/Curitiba/place/p/10805072/IGO+-+Instituto+Guskuma+de+Odontologia+-+Curitiba</t>
+          <t>https://openguessr.com/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(41) 3359-4884</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>55413359488400</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/IGO%20curitiba</t>
+          <t>https://www.google.com/maps/search/OpenGuessr%20curitiba</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da IGO aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da OpenGuessr aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -934,29 +930,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a IGO?</t>
+Posso te mandar a prévia demonstrativa que fiz para a OpenGuessr?</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://wa.me/55413359488400?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20IGO%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OpenGuessr%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://wa.me/55413359488400?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20IGO%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OpenGuessr%3F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>curitiba.pr.gov.br</t>
+          <t>Guess Where You Are</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>curitiba.pr.gov.br</t>
+          <t>Guess Where You Are - Free GeoGuessr Alternative</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -971,7 +967,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Solicite aqui seu acesso a prefeitura de Curitiba....</t>
+          <t>community World (upload your map files to the Google doc)....</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -981,24 +977,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.curitiba.pr.gov.br/</t>
+          <t>https://guesswhereyouare.com/</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/curitiba.pr.gov.br%20curitiba</t>
+          <t>https://www.google.com/maps/search/Guess%20Where%20You%20Are%20curitiba</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da curitiba.pr.gov.br aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Guess Where You Are aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1008,29 +1004,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a curitiba.pr.gov.br?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Guess Where You Are?</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=curitiba.pr.gov.br%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Guess%20Where%20You%20Are%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=curitiba.pr.gov.br%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Guess%20Where%20You%20Are%3F</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Como RASTREAR un CELULAR por GOOGLE MAPS...</t>
+          <t>Clnica Felpe Odontologia Curitiba</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Como RASTREAR un CELULAR por GOOGLE MAPS... - YouTube</t>
+          <t>Clínica Felpe Odontologia Curitiba</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1045,34 +1041,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hoy te enseñaré como rastrear un celular por google maps con varios dispositivos tecnológicos.Espero...</t>
+          <t>Whatsapp Felpe Odontologia.Clínica Ortodôntica Curitiba. ORTODONTIA. Mostre o seu melhor sorriso e c...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.felpe.com.br/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>41997321</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5541997321</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Como%20RASTREAR%20un%20CELULAR%20por%20GOOGLE%20MAPS...%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnica%20Felpe%20Odontologia%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Como RASTREAR un CELULAR por GOOGLE MAPS... aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Clnica Felpe Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1082,29 +1082,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Como RASTREAR un CELULAR por GOOGLE MAPS...?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Felpe Odontologia Curitiba?</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Como%20RASTREAR%20un%20CELULAR%20por%20GOOGLE%20MAPS...%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541997321?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Felpe%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Como%20RASTREAR%20un%20CELULAR%20por%20GOOGLE%20MAPS...%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541997321?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Felpe%20Odontologia%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>UpClin Odontologia Curitiba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Google Maps</t>
+          <t>UpClin Odontologia Curitiba</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1119,38 +1119,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Find local businesses, view maps and get driving directions in Google Maps....</t>
+          <t>Odontologia Curitiba, Odontopediatria, Ortodontia, Cirurgia Buco-Maxilo, Dentista Clínico Geral.O ra...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.upclin.com/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(11) 91234-5678</t>
+          <t>(41) 3095-9660</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>551191234567800</t>
+          <t>554130959660</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Google%20Maps%20curitiba</t>
+          <t>https://www.google.com/maps/search/UpClin%20Odontologia%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Google Maps aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da UpClin Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1160,29 +1160,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Google Maps?</t>
+Posso te mandar a prévia demonstrativa que fiz para a UpClin Odontologia Curitiba?</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://wa.me/551191234567800?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Google%20Maps%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554130959660?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20UpClin%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://wa.me/551191234567800?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Google%20Maps%3F</t>
+          <t>https://wa.me/554130959660?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20UpClin%20Odontologia%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>"Dental clinic" in Curitiba</t>
+          <t>SV Odontologia • Tratamento Invisalign e Orto</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"Dental clinic" in Curitiba - Search in Google Maps</t>
+          <t>SV Odontologia • Tratamento Invisalign e Ortodontia • Curitiba PR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1197,38 +1197,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>You're seeing a limited view of Google Maps. Mappi Odontologia - Boa Vista, Mappi Odontologia - Cent...</t>
+          <t>A SV Odontologia está comprometida em oferecer aos seus pacientes o melhor tratamento ortodôntico po...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.svodontologia.com.br/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>41 99572-0198</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>554199572019800</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/%22Dental%20clinic%22%20in%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20curitiba</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da "Dental clinic" in Curitiba aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da SV Odontologia • Tratamento Invisalign e Orto aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1238,29 +1234,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a "Dental clinic" in Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a SV Odontologia • Tratamento Invisalign e Orto?</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://wa.me/554199572019800?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20%22Dental%20clinic%22%20in%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://wa.me/554199572019800?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20%22Dental%20clinic%22%20in%20Curitiba%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%3F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Odontologia</t>
+          <t>Pinho Odontologia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Odontologia em Curitiba | Murano Odontologia (41) 3253-1907 ...</t>
+          <t>Pinho Odontologia | Curitiba - PR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1275,7 +1271,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A Clínica Murano Odontologia de Referência dá bons motivos para você ter um sorriso bonito e saudáve...</t>
+          <t>Clínica odontológica em Curitiba. Especialistas em implantes, ortodontia, invisalign, odontopediatri...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1285,28 +1281,28 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://muranoodontologia.com.br/</t>
+          <t>https://drpinho.com.br/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(41) 3253-1907</t>
+          <t>(41) 3342-2121</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>55413253190700</t>
+          <t>554133422121</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Pinho%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Pinho Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1316,29 +1312,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Pinho Odontologia?</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://wa.me/55413253190700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554133422121?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Pinho%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://wa.me/55413253190700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%3F</t>
+          <t>https://wa.me/554133422121?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Pinho%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Dental Esthetic Center / odontologia curitiba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Curitiba - Centro - PR - Mappi Odontologia</t>
+          <t>Dental Esthetic Center / odontologia curitiba - YouTube</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1353,34 +1349,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Conheça a unidade da Mappi no centro de Curitiba/PR e agende a sua avaliação agora mesmo para conqui...</t>
+          <t>Vídeos produzidos pela Dental Esthetic Center by Rogério Marcondes sobre Odontologia Estética, proce...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://mappiodontologia.com.br/curitiba-centro-pr/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(41) 99280-3875</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5541992803875</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dental Esthetic Center / odontologia curitiba aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1390,29 +1390,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dental Esthetic Center / odontologia curitiba?</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541992803875?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541992803875?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dra.Keslen_Geffer</t>
+          <t>Cury Clnica Odontolgica</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dra.Keslen_Geffer | Instagram | Linktree</t>
+          <t>Cury Clínica Odontológica</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,34 +1427,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@Dra.Keslen_Geffer. Odontologia de excelência em Curitiba. Google Maps - 5.0. Agende sua Consulta. I...</t>
+          <t>Clínica odontológica em Curitiba com espaço amplo e moderno, projetado para a oferecer toda a estrut...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://ortodontiacuritiba.com.br/</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dra.Keslen_Geffer%20curitiba</t>
+          <t>https://www.google.com/maps/search/Cury%20Clnica%20Odontolgica%20curitiba</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dra.Keslen_Geffer aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Cury Clnica Odontolgica aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1464,29 +1464,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dra.Keslen_Geffer?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Cury Clnica Odontolgica?</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dra.Keslen_Geffer%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Cury%20Clnica%20Odontolgica%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dra.Keslen_Geffer%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Cury%20Clnica%20Odontolgica%3F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Link to instagram.com</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Home - Fahl Center</t>
+          <t>Link to instagram.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,38 +1501,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Centro educacional pioneiro em Odontologia Estética de excelência que une arte e ciência em sua meto...</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://fahl.com.br/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41 99961 7268</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>554199961726800</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Home%20curitiba</t>
+          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20curitiba</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Home aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Link to instagram.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1542,29 +1538,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Home?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://wa.me/554199961726800?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Home%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20instagram.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://wa.me/554199961726800?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Home%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20instagram.com%3F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Encontrar seu smartphone</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Encontrar seu smartphone</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,12 +1575,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Configurações da Conta do Google. Ajuda. Fazer login....</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1594,19 +1590,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Encontrar%20seu%20smartphone%20curitiba</t>
+          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20curitiba</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Encontrar seu smartphone aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Link to facebook.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1616,29 +1612,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Encontrar seu smartphone?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Encontrar%20seu%20smartphone%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Encontrar%20seu%20smartphone%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OpenGuessr</t>
+          <t>Clnicas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OpenGuessr - Error</t>
+          <t>Clínicas em Curitiba de Odontologia | Doctuo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1653,7 +1649,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Openguessr - guess the country based off Google maps....</t>
+          <t>Clínicas de Odontologia em Curitiba.Rua Eunice Bettini Bartoszeck , 1151, Curitiba, Paraná. Uniodont...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1663,24 +1659,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://openguessr.com/</t>
+          <t>https://www.doctuo.com.br/centros-medicos/odontologia/curitiba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(34) 3411-4813</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>553434114813</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/OpenGuessr%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnicas%20curitiba</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da OpenGuessr aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnicas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1690,29 +1690,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a OpenGuessr?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnicas?</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=OpenGuessr%20curitiba%20whatsapp</t>
+          <t>https://wa.me/553434114813?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnicas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=OpenGuessr%20curitiba%20whatsapp</t>
+          <t>https://wa.me/553434114813?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnicas%3F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Clnica Felpe Odontologia Curitiba</t>
+          <t>Centro Clinico Vidaclin Odontologia, Curitiba</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clínica Felpe Odontologia Curitiba</t>
+          <t>Centro Clinico Vidaclin Odontologia, Curitiba — R. Urbâno Lopes..</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Whatsapp Felpe Odontologia.Clínica Ortodôntica Curitiba. ORTODONTIA. Mostre o seu melhor sorriso e c...</t>
+          <t>Centro Clinico Vidaclin Odontologia, endereço — R. Urbâno Lopes, 89 - Cristo Rei, Curitiba - PR, 800...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1737,24 +1737,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.felpe.com.br/</t>
+          <t>https://br.polomap.com/curitiba/32560</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(41) 3362-7654</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>554133627654</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Felpe%20Odontologia%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Centro%20Clinico%20Vidaclin%20Odontologia%2C%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Felpe Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Centro Clinico Vidaclin Odontologia, Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1764,29 +1768,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Felpe Odontologia Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Centro Clinico Vidaclin Odontologia, Curitiba?</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Felpe%20Odontologia%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554133627654?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Centro%20Clinico%20Vidaclin%20Odontologia%2C%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnica%20Felpe%20Odontologia%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554133627654?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Centro%20Clinico%20Vidaclin%20Odontologia%2C%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Consultorio Odontologico Santa Lucia S/s</t>
+          <t>Clnica odontolgica de Curitiba</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Consultorio Odontologico Santa Lucia S/s em Curitiba, PR | Solutu</t>
+          <t>Clínica odontológica de Curitiba - Odontologia Curitiba, PR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1801,7 +1805,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A empresa Consultorio Odontologico Santa Lucia S/s trabalha há mais de 26 anos na categoria Odontolo...</t>
+          <t>Odontologia &amp; Harmonização facial, Curitiba. (41) 4101-3337.Conheça a Clínica Odontológica. Localiza...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1811,28 +1815,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.solutudo.com.br/empresas/pr/curitiba/odontologia/consultorio-odontologico-santa-lucia-s-s-2821967</t>
+          <t>https://taiatellaodontologia.com.br/clinica-odontologica-odontologia-curitiba.html</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(41) 32523537</t>
+          <t>(41) 4101-3337</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>55413252353700</t>
+          <t>554141013337</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Consultorio%20Odontologico%20Santa%20Lucia%20S/s%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnica%20odontolgica%20de%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Consultorio Odontologico Santa Lucia S/s aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica odontolgica de Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1842,29 +1846,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Consultorio Odontologico Santa Lucia S/s?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica odontolgica de Curitiba?</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://wa.me/55413252353700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultorio%20Odontologico%20Santa%20Lucia%20S/s%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554141013337?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20odontolgica%20de%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://wa.me/55413252353700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultorio%20Odontologico%20Santa%20Lucia%20S/s%3F</t>
+          <t>https://wa.me/554141013337?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20odontolgica%20de%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UpClin Odontologia Curitiba</t>
+          <t>105 Odontologia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UpClin Odontologia Curitiba</t>
+          <t>105 Odontologia - Curitiba - PR - Somos Popular</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1879,38 +1883,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Odontologia Curitiba, Odontopediatria, Ortodontia, Cirurgia Buco-Maxilo, Dentista Clínico Geral.O ra...</t>
+          <t>105 Odontologia - Curitiba - PR. Clínica Popular com preços muito mais acessíveis.Endereço: Avenida ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR (ERRO 404) 🚨</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.upclin.com/</t>
+          <t>https://www.somospopular.com.br/hospitais-e-ambulatorios/105-odontologia-curitiba-pr/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5541998225</t>
+          <t>41301027</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>554199822500</t>
+          <t>5541301027</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/UpClin%20Odontologia%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/105%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da UpClin Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 105 Odontologia aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1920,29 +1924,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a UpClin Odontologia Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 105 Odontologia?</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://wa.me/554199822500?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20UpClin%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541301027?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20105%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://wa.me/554199822500?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20UpClin%20Odontologia%20Curitiba%3F</t>
+          <t>https://wa.me/5541301027?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20105%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SV Odontologia • Tratamento Invisalign e Orto</t>
+          <t>Mandic</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SV Odontologia • Tratamento Invisalign e Ortodontia • Curitiba PR</t>
+          <t>Mandic - Curitiba | São Leopoldo Mandic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1957,7 +1961,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>A SV Odontologia está comprometida em oferecer aos seus pacientes o melhor tratamento ortodôntico po...</t>
+          <t>A Unidade de Curitiba da Faculdade São Leopoldo Mandic existe desde 2003, e segue deixando sua marca...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1967,24 +1971,28 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.svodontologia.com.br/</t>
+          <t>https://slmandic.edu.br/unidade/curitiba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(09) 2457-2000</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>550924572000</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20curitiba</t>
+          <t>https://www.google.com/maps/search/Mandic%20curitiba</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da SV Odontologia • Tratamento Invisalign e Orto aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Mandic aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1994,29 +2002,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a SV Odontologia • Tratamento Invisalign e Orto?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Mandic?</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20curitiba%20whatsapp</t>
+          <t>https://wa.me/550924572000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Mandic%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20curitiba%20whatsapp</t>
+          <t>https://wa.me/550924572000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Mandic%3F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pinho Odontologia</t>
+          <t>Sorri Dente Odontologia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pinho Odontologia | Curitiba - PR</t>
+          <t>Sorri Dente Odontologia - Curitiba - PR - Consultório</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2031,7 +2039,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Clínica odontológica em Curitiba. Especialistas em implantes, ortodontia, invisalign, odontopediatri...</t>
+          <t>Sorri Dente Odontologia - Centro - Curitiba - PR - Saúde Bucal.Estabelecimento do Tipo: Consultório....</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2041,24 +2049,28 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://drpinho.com.br/</t>
+          <t>https://cebes.com.br/sorri-dente-odontologia-1078542/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(41) 99976-7375</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5541999767375</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Pinho%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Sorri%20Dente%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Pinho Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Sorri Dente Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2068,29 +2080,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Pinho Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Sorri Dente Odontologia?</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Pinho%20Odontologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541999767375?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Sorri%20Dente%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Pinho%20Odontologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541999767375?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Sorri%20Dente%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dental Esthetic Center / odontologia curitiba</t>
+          <t>Arch Odontologia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dental Esthetic Center / odontologia curitiba - YouTube</t>
+          <t>Arch Odontologia | Curitiba | Clínica Odontológica</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2105,38 +2117,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vídeos produzidos pela Dental Esthetic Center by Rogério Marcondes sobre Odontologia Estética, proce...</t>
+          <t>Aqui na Arch Odontologia, você encontra os mais modernos tratamentos estéticos odontológicos: faceta...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.archodontologia.com/</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(41) 99280-3875</t>
+          <t>(41) 3022-2999</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>554199280387500</t>
+          <t>554130222999</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Arch%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dental Esthetic Center / odontologia curitiba aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Arch Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2146,29 +2158,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dental Esthetic Center / odontologia curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Arch Odontologia?</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://wa.me/554199280387500?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554130222999?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Arch%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://wa.me/554199280387500?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%3F</t>
+          <t>https://wa.me/554130222999?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Arch%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>novo</t>
+          <t>Bittencourt Odontologia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>home-novo - CEOPAR - Centro de Estética Oral Paraná</t>
+          <t>Bittencourt Odontologia | Dentistas em Curitiba | Paraná</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2183,7 +2195,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clínica Odontológica em Curitiba. São mais de 10.000 casos concluídos, do implante à ortodontia.A es...</t>
+          <t>Bem-Vindo(a) à Bittencourt Odontologia. Atendimento Completo Para Toda Família! Temos uma equipe de ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2193,24 +2205,28 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://ceoparana.com.br/</t>
+          <t>https://www.bittencourtodontologia.com.br/</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(19) 3816-7455</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>551938167455</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/novo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Bittencourt%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da novo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Bittencourt Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2220,29 +2236,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a novo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Bittencourt Odontologia?</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=novo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/551938167455?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bittencourt%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=novo%20curitiba%20whatsapp</t>
+          <t>https://wa.me/551938167455?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bittencourt%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cury Clnica Odontolgica</t>
+          <t>Citag Odontologia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cury Clínica Odontológica</t>
+          <t>Citag Odontologia – O sorriso dos sonhos, pra você!</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2257,7 +2273,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Clínica odontológica em Curitiba com espaço amplo e moderno, projetado para a oferecer toda a estrut...</t>
+          <t>Diferenciais da Citag Odontologia. Entenda o porque somos referência na Odontologia em Curitiba! Pro...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2267,28 +2283,28 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://ortodontiacuritiba.com.br/</t>
+          <t>https://citagodontologia.com.br/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41 3015-0841</t>
+          <t>(47) 1562-3100</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>55413015084100</t>
+          <t>554715623100</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Cury%20Clnica%20Odontolgica%20curitiba</t>
+          <t>https://www.google.com/maps/search/Citag%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Cury Clnica Odontolgica aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Citag Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2298,29 +2314,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Cury Clnica Odontolgica?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Citag Odontologia?</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://wa.me/55413015084100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Cury%20Clnica%20Odontolgica%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554715623100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Citag%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://wa.me/55413015084100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Cury%20Clnica%20Odontolgica%3F</t>
+          <t>https://wa.me/554715623100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Citag%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Dra. Izabela Taiatella</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Dra. Izabela Taiatella - Odontologia em CURITIBA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2335,38 +2351,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Dra. Izabela Taiatella - Odontologia e Harmonização facial, Curitiba - Uma profissional altamente qu...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://taiatellaodontologia.com.br/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>41 98420-4581</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>554198420458100</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dra.%20Izabela%20Taiatella%20curitiba</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to facebook.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Dra. Izabela Taiatella aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2376,29 +2388,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dra. Izabela Taiatella?</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://wa.me/554198420458100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra.%20Izabela%20Taiatella%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://wa.me/554198420458100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra.%20Izabela%20Taiatella%3F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Fujikawa Odontologia Dentista</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Fujikawa Odontologia Dentista em Curitiba. Atendemos plano AMIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2413,34 +2425,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Entre em contato conosco por telefone, formulário de contato ou Whatsapp que retornaremos com priori...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://fujikawaodontologia.com.br/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(41) 98825-8833</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5541988258833</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20curitiba</t>
+          <t>https://www.google.com/maps/search/Fujikawa%20Odontologia%20Dentista%20curitiba</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to instagram.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Fujikawa Odontologia Dentista aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2450,29 +2466,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Fujikawa Odontologia Dentista?</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Link%20to%20instagram.com%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988258833?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Fujikawa%20Odontologia%20Dentista%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Link%20to%20instagram.com%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988258833?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Fujikawa%20Odontologia%20Dentista%3F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Clnicas</t>
+          <t>Clinident</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clínicas em Curitiba de Odontologia | Doctuo</t>
+          <t>Clinident | Clínica Odontológica em Curitiba desde 1968</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2487,7 +2503,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Clínicas de Odontologia em Curitiba.Rua Eunice Bettini Bartoszeck , 1151, Curitiba, Paraná. Uniodont...</t>
+          <t>Na Clinident, você encontra atendimento odontológico completo em Curitiba, com emergência, raio-X od...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2497,24 +2513,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.doctuo.com.br/centros-medicos/odontologia/curitiba</t>
+          <t>https://clinident24h.com.br/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnicas%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clinident%20curitiba</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnicas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clinident aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2524,29 +2540,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnicas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clinident?</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnicas%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clinident%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clnicas%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clinident%3F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Implantes Dentrios e Prtese Protocolo</t>
+          <t>Clinident 24 Horas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Implantes Dentários e Prótese Protocolo em Curitiba</t>
+          <t>Clinident 24 Horas - Dentista 24 Horas em Curitiba | dentista ...</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2561,7 +2577,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Clínica de Ortodontia e Implantodontia em Curitiba, Implantes e Aparelhos Dentários Transparentes e ...</t>
+          <t>Fornecemos atendimento odontológico abrangente, com uma equipe preparada para oferecer o melhor serv...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2571,28 +2587,28 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://debocaaberta.com.br/</t>
+          <t>https://clinident24h.com.br/contato.html</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(41) 98485-1212</t>
+          <t>(41) 3264-1984</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>554198485121200</t>
+          <t>554132641984</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Implantes%20Dentrios%20e%20Prtese%20Protocolo%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clinident%2024%20Horas%20curitiba</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Implantes Dentrios e Prtese Protocolo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clinident 24 Horas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2602,29 +2618,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Implantes Dentrios e Prtese Protocolo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clinident 24 Horas?</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://wa.me/554198485121200?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Implantes%20Dentrios%20e%20Prtese%20Protocolo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554132641984?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clinident%2024%20Horas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://wa.me/554198485121200?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Implantes%20Dentrios%20e%20Prtese%20Protocolo%3F</t>
+          <t>https://wa.me/554132641984?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clinident%2024%20Horas%3F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10 melhores dentistas para Curitiba</t>
+          <t>Odonto Pio XII</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10 melhores dentistas para Curitiba</t>
+          <t>Odonto Pio XII - Seu dentista 24h em Curitiba</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2639,7 +2655,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>80020-340 Curitiba. Mestre e Doutorando em Odontologia Clínica, especialista em tratamentos estético...</t>
+          <t>Localizado no centro de Curitiba, região de fácil acesso para pacientes de todas as regiões da cidad...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2649,24 +2665,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.starofservice.com.br/dir/parana/curitiba/curitiba/servicos-dentarios</t>
+          <t>https://www.odontopioxii.com.br/</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/10%20melhores%20dentistas%20para%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Odonto%20Pio%20XII%20curitiba</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 10 melhores dentistas para Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odonto Pio XII aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2676,29 +2692,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 10 melhores dentistas para Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odonto Pio XII?</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=10%20melhores%20dentistas%20para%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odonto%20Pio%20XII%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=10%20melhores%20dentistas%20para%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odonto%20Pio%20XII%3F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dentista Ortodontista Invisalign Curitiba</t>
+          <t>Egao Odontologia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dentista Ortodontista Invisalign Curitiba - Barusso</t>
+          <t>Egao Odontologia - Dentista em Curitiba - PR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2713,7 +2729,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blog e Últimas Notícias Sobre a Odontologia em Curitiba. Acompanhe o nosso conteúdo e aprenda mais s...</t>
+          <t>Com a chancela do Dr. Carlos Shiratori, a Egao Odontologia conta com mais de duas décadas de atendim...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2723,24 +2739,28 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://barussodontologia.com.br/</t>
+          <t>https://egao.com.br/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(41) 3257-1026</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>554132571026</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%20Ortodontista%20Invisalign%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Egao%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista Ortodontista Invisalign Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Egao Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2750,29 +2770,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista Ortodontista Invisalign Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Egao Odontologia?</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentista%20Ortodontista%20Invisalign%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554132571026?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Egao%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentista%20Ortodontista%20Invisalign%20Curitiba%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554132571026?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Egao%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clinica Premium Curitiba</t>
+          <t>Dentista Ortodontista Invisalign Curitiba</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Clinica Premium Curitiba</t>
+          <t>Dentista Ortodontista Invisalign Curitiba - Barusso</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2787,7 +2807,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nicolle Duza, nossa clínica é reconhecida por sua abordagem inovadora e humanizada na odontologia.Me...</t>
+          <t>Conheça alguns tratamentos Odontológicos Ortodontia Dentista Ortodontista. Aparelhos fixos e removív...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2797,28 +2817,28 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://clinicapremiumcuritiba.com.br/</t>
+          <t>https://barussodontologia.com.br/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5541996498</t>
+          <t>(41) 99128-7722</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>554199649800</t>
+          <t>5541991287722</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clinica%20Premium%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dentista%20Ortodontista%20Invisalign%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clinica Premium Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentista Ortodontista Invisalign Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2828,29 +2848,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clinica Premium Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista Ortodontista Invisalign Curitiba?</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://wa.me/554199649800?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clinica%20Premium%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541991287722?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20Ortodontista%20Invisalign%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://wa.me/554199649800?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clinica%20Premium%20Curitiba%3F</t>
+          <t>https://wa.me/5541991287722?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20Ortodontista%20Invisalign%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dentistas</t>
+          <t>Odonto Kennedy Centro Odontolgico</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dentistas em Curitiba - PR: 2195 avaliados · 4.8 | DentMap</t>
+          <t>Odonto Kennedy Centro Odontológico</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2865,7 +2885,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2324 dentistas em Curitiba, PR em 27 bairros. Nota média 4.8. Veja WhatsApp e telefone, compare aval...</t>
+          <t>Odonto Kennedy. 41 99595-1636. contato@odontokennedy.com.br. Instagram.Odontologia. Curitiba. Mude d...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2875,24 +2895,28 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://dentmap.com.br/dentistas/curitiba</t>
+          <t>https://odontokennedy.com.br/</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(41) 99595-1636</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5541995951636</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentistas%20curitiba</t>
+          <t>https://www.google.com/maps/search/Odonto%20Kennedy%20Centro%20Odontolgico%20curitiba</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentistas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odonto Kennedy Centro Odontolgico aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2902,29 +2926,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentistas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odonto Kennedy Centro Odontolgico?</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentistas%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541995951636?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odonto%20Kennedy%20Centro%20Odontolgico%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dentistas%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541995951636?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odonto%20Kennedy%20Centro%20Odontolgico%3F</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Innova Clinica Medica E Odontologica Ss</t>
+          <t>Barbearia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Innova Clinica Medica E Odontologica Ss em Curitiba, PR | Solutud</t>
+          <t>Barbearia em Curitiba - perto de mim - Cabeleireiro masculino ...</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2939,7 +2963,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Veja informações, telefones, endereços, vagas de emprego, produtos, ofertas, eventos e muito mais.Cu...</t>
+          <t>Um recurso incrível que você pode utilizar é o nosso mapa virtual, em que você pode encontrar todas ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2949,24 +2973,28 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.solutudo.com.br/empresas/pr/curitiba/odontologia/innova-clinica-medica-e-odontologica-ss-2877477</t>
+          <t>https://booksy.com/pt-br/s/barbearias/583853_curitiba</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(41) 99861-8127</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5541998618127</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Innova%20Clinica%20Medica%20E%20Odontologica%20Ss%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Innova Clinica Medica E Odontologica Ss aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2976,29 +3004,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Innova Clinica Medica E Odontologica Ss?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia?</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Innova%20Clinica%20Medica%20E%20Odontologica%20Ss%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541998618127?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Innova%20Clinica%20Medica%20E%20Odontologica%20Ss%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541998618127?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Clnica odontolgica de Curitiba</t>
+          <t>barbearias</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Clínica odontológica de Curitiba - Odontologia Curitiba, PR</t>
+          <t>barbearias em Curitiba 2026 | OndeAbrir</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3013,7 +3041,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odontologia &amp; Harmonização facial, Curitiba. (41) 4101-3337.Conheça a Clínica Odontológica. Localiza...</t>
+          <t>Panorama competitivo: barbearias em Curitiba. Curitiba tem 1.8M habitantes e um mercado de barbearia...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3023,28 +3051,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://taiatellaodontologia.com.br/clinica-odontologica-odontologia-curitiba.html</t>
+          <t>https://ondeabrir.com/mercado/barbearia/curitiba</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(41) 4101-3337</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>55414101333700</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20odontolgica%20de%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/barbearias%20curitiba</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica odontolgica de Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3054,29 +3078,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica odontolgica de Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a barbearias?</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://wa.me/55414101333700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20odontolgica%20de%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://wa.me/55414101333700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20odontolgica%20de%20Curitiba%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20barbearias%3F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Arch Odontologia</t>
+          <t>Barbearia Clube</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Arch Odontologia | Curitiba | Clínica Odontológica</t>
+          <t>Barbearia Clube | Tradição e Excelência em Curitiba (Mercês)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3091,7 +3115,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aqui na Arch Odontologia, você encontra os mais modernos tratamentos estéticos odontológicos: faceta...</t>
+          <t>A barbearia clássica preferida de Curitiba. Barbearia Clube: Barba na navalha, cortes visagistas, Di...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3101,24 +3125,28 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.archodontologia.com/</t>
+          <t>https://barbeariaclube.com.br/</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(41) 3014-9413</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>554130149413</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Arch%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20Clube%20curitiba</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Arch Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia Clube aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3128,29 +3156,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Arch Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Clube?</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Arch%20Odontologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554130149413?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Clube%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Arch%20Odontologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554130149413?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Clube%3F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bittencourt Odontologia</t>
+          <t>CNPJ 53.441.822/0001-74</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bittencourt Odontologia | Dentistas em Curitiba | Paraná</t>
+          <t>CNPJ 53.441.822/0001-74 - barbearia curitiba ltda | CNPJ go!</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3165,7 +3193,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bem-Vindo(a) à Bittencourt Odontologia. Atendimento Completo Para Toda Família! Temos uma equipe de ...</t>
+          <t>Enriqueça empresas com Google Maps, Instagram, LinkedIn e mais. A IA gera pitchs personalizados para...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3175,24 +3203,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.bittencourtodontologia.com.br/</t>
+          <t>https://cnpjgo.com.br/cnpj/53441822000174</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bittencourt%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/CNPJ%2053.441.822/0001-74%20curitiba</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Bittencourt Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da CNPJ 53.441.822/0001-74 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3202,29 +3230,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Bittencourt Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a CNPJ 53.441.822/0001-74?</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Bittencourt%20Odontologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%2053.441.822/0001-74%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Bittencourt%20Odontologia%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%2053.441.822/0001-74%3F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dra. Izabela Taiatella</t>
+          <t>Victor Hugo Barbeiro da Lenno Barbearia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dra. Izabela Taiatella - Odontologia em CURITIBA</t>
+          <t>Victor Hugo Barbeiro da Lenno Barbearia - Curitiba 2017 - YouTube</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3239,34 +3267,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dra. Izabela Taiatella - Odontologia e Harmonização facial, Curitiba - Uma profissional altamente qu...</t>
+          <t>© 2025 Google LLC....</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://taiatellaodontologia.com.br/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(42) 2590-7400</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>554225907400</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dra.%20Izabela%20Taiatella%20curitiba</t>
+          <t>https://www.google.com/maps/search/Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dra. Izabela Taiatella aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Victor Hugo Barbeiro da Lenno Barbearia aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3276,29 +3308,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dra. Izabela Taiatella?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Victor Hugo Barbeiro da Lenno Barbearia?</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dra.%20Izabela%20Taiatella%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554225907400?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dra.%20Izabela%20Taiatella%20curitiba%20whatsapp</t>
+          <t>https://wa.me/554225907400?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Citag Odontologia</t>
+          <t>Barbearia Saint Germain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Citag Odontologia – O sorriso dos sonhos, pra você!</t>
+          <t>Barbearia Saint Germain em Curitiba, PR | MestreGeo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3313,7 +3345,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Diferenciais da Citag Odontologia. Entenda o porque somos referência na Odontologia em Curitiba! Pro...</t>
+          <t>Informações completas da organização BARBEARIA SAINT GERMAIN LTDA em Curitiba, Paraná. CNPJ: 36.748....</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3323,28 +3355,28 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://citagodontologia.com.br/</t>
+          <t>https://mestregeo.com.br/cnpj/pr/curitiba/barbearia-saint-germain-36748126000196</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4715623100</t>
+          <t>(41) 99894-4124</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>55471562310000</t>
+          <t>5541998944124</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Citag%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20Saint%20Germain%20curitiba</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Citag Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia Saint Germain aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3354,29 +3386,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Citag Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Saint Germain?</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://wa.me/55471562310000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Citag%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541998944124?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Saint%20Germain%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://wa.me/55471562310000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Citag%20Odontologia%3F</t>
+          <t>https://wa.me/5541998944124?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Saint%20Germain%3F</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unik Odontologia</t>
+          <t>Barbearias / Barbeiros</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Unik Odontologia – Clínica odontológica</t>
+          <t>Barbearias / Barbeiros em Curitiba, PR — WhatsApp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3391,38 +3423,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Entre em Contato Conosco. R. Paulo Setúbal, 3280 Hauer, Curitiba - PR. (41) 3408-5222. contato@uniko...</t>
+          <t>Veja os barbeiros mais bem avaliados em Curitiba, PR. Corte masculino, barba, degradê, navalhado e t...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://unikodontologia.com/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(41) 3408-5222</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>55413408522200</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Unik%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearias%20/%20Barbeiros%20curitiba</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Unik Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearias / Barbeiros aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3432,29 +3460,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Unik Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearias / Barbeiros?</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://wa.me/55413408522200?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Unik%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearias%20/%20Barbeiros%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://wa.me/55413408522200?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Unik%20Odontologia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearias%20/%20Barbeiros%3F</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fujikawa Odontologia Dentista</t>
+          <t>15 Melhores Barbearias no gua Verde</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fujikawa Odontologia Dentista em Curitiba. Atendemos plano AMIL</t>
+          <t>15 Melhores Barbearias no Água Verde em Curitiba — Guia... | Bear</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3469,7 +3497,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Entre em contato conosco por telefone, formulário de contato ou Whatsapp que retornaremos com priori...</t>
+          <t>8. Kennedy Barbearia | Barbearia Água Verde Curitiba. 9. Mr. Capelli Barber shop.Destacam-se a Barbe...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3479,24 +3507,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://fujikawaodontologia.com.br/</t>
+          <t>https://blog.beard.com.br/barbearias-no-agua-verde-curitiba/</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Fujikawa%20Odontologia%20Dentista%20curitiba</t>
+          <t>https://www.google.com/maps/search/15%20Melhores%20Barbearias%20no%20gua%20Verde%20curitiba</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Fujikawa Odontologia Dentista aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 15 Melhores Barbearias no gua Verde aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3506,29 +3534,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Fujikawa Odontologia Dentista?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 15 Melhores Barbearias no gua Verde?</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Fujikawa%20Odontologia%20Dentista%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2015%20Melhores%20Barbearias%20no%20gua%20Verde%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Fujikawa%20Odontologia%20Dentista%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2015%20Melhores%20Barbearias%20no%20gua%20Verde%3F</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Clinident</t>
+          <t>CNPJ: 18.553.536/0001-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Clinident | Clínica Odontológica em Curitiba desde 1968</t>
+          <t>CNPJ: 18.553.536/0001-08 - Barbearia Curitiba Ltda - Nacional...</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3543,7 +3571,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Na Clinident, você encontra atendimento odontológico completo em Curitiba, com emergência, raio-X od...</t>
+          <t>O CNPJ da empresa Barbearia Curitiba Ltda (Barbearia Clube) é 18.553.536/0001-08. Com sede em CURITI...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3553,24 +3581,28 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://clinident24h.com.br/</t>
+          <t>https://www.nacionalconsultas.com.br/cnpj/barbearia-curitiba-ltda-18553536000108</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(02) 5581-5700</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>550255815700</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clinident%20curitiba</t>
+          <t>https://www.google.com/maps/search/CNPJ%3A%2018.553.536/0001-08%20curitiba</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clinident aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da CNPJ: 18.553.536/0001-08 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3580,29 +3612,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clinident?</t>
+Posso te mandar a prévia demonstrativa que fiz para a CNPJ: 18.553.536/0001-08?</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clinident%20curitiba%20whatsapp</t>
+          <t>https://wa.me/550255815700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%3A%2018.553.536/0001-08%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clinident%20curitiba%20whatsapp</t>
+          <t>https://wa.me/550255815700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%3A%2018.553.536/0001-08%3F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Odonto Pio XII</t>
+          <t>CNPJ: 37.393.890/0001-59</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Odonto Pio XII - Seu dentista 24h em Curitiba</t>
+          <t>CNPJ: 37.393.890/0001-59 - La Mafia Social Club Barbearia Curitib</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3617,7 +3649,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Localizado no centro de Curitiba, região de fácil acesso para pacientes de todas as regiões da cidad...</t>
+          <t>O CNPJ da empresa La Mafia Social Club Barbearia Curitiba Ltda. é 37.393.890/0001-59. Com sede em CU...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3627,24 +3659,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.odontopioxii.com.br/</t>
+          <t>https://www.informecadastral.com.br/cnpj/la-mafia-social-club-barbearia-curitiba-ltda-37393890000159</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odonto%20Pio%20XII%20curitiba</t>
+          <t>https://www.google.com/maps/search/CNPJ%3A%2037.393.890/0001-59%20curitiba</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odonto Pio XII aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da CNPJ: 37.393.890/0001-59 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3654,29 +3686,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odonto Pio XII?</t>
+Posso te mandar a prévia demonstrativa que fiz para a CNPJ: 37.393.890/0001-59?</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Odonto%20Pio%20XII%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%3A%2037.393.890/0001-59%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Odonto%20Pio%20XII%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%3A%2037.393.890/0001-59%3F</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Clinident 24 Horas</t>
+          <t>Os melhores barbeiros perto de mim</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Clinident 24 Horas - Dentista 24 Horas em Curitiba | dentista ...</t>
+          <t xml:space="preserve">Os melhores barbeiros perto de mim em Curitiba - FreshaBarbearia </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3691,7 +3723,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fornecemos atendimento odontológico abrangente, com uma equipe preparada para oferecer o melhor serv...</t>
+          <t>Agendar online com os melhores Barbeiros perto de você em Curitiba. Excelentes ofertas e descontos! ...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3701,24 +3733,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://clinident24h.com.br/contato.html</t>
+          <t>https://www.fresha.com/lp/pt/bt/barbearias/br-curitiba</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>WhatsApp no Maps 📍</t>
+          <t>(CU) 98877-6655</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clinident%2024%20Horas%20curitiba</t>
+          <t>https://www.google.com/maps/search/Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clinident 24 Horas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Os melhores barbeiros perto de mim aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3728,403 +3760,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clinident 24 Horas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Os melhores barbeiros perto de mim?</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clinident%2024%20Horas%20curitiba%20whatsapp</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20melhores%20barbeiros%20perto%20de%20mim%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Clinident%2024%20Horas%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Egao Odontologia</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Egao Odontologia - Dentista em Curitiba - PR</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Com a chancela do Dr. Carlos Shiratori, a Egao Odontologia conta com mais de duas décadas de atendim...</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://egao.com.br/</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>41999998888</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>554199999888800</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Egao%20Odontologia%20curitiba</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Egao Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Egao Odontologia?</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://wa.me/554199999888800?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Egao%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>https://wa.me/554199999888800?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Egao%20Odontologia%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Contato</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Contato - Odhos Odontologia Personalizada</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Nosso compromisso com a ética, profissionalismo e saúde bucal transformou a Odhos em uma referência ...</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://odhos.com.br/contato/</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>WhatsApp no Maps 📍</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Contato%20curitiba</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Contato aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Contato?</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Contato%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Contato%20curitiba%20whatsapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Maxiclin Odontologia Curitiba</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Maxiclin Odontologia Curitiba | Excelência em Odontologia</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>A Maxiclin é uma clínica de odontologia em Curitiba que oferece atendimento odontológico interdiscip...</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.maxiclin.com.br/</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(41) 98519-4512</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>554198519451200</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Maxiclin%20Odontologia%20Curitiba%20curitiba</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Maxiclin Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Maxiclin Odontologia Curitiba?</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>https://wa.me/554198519451200?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Maxiclin%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>https://wa.me/554198519451200?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Maxiclin%20Odontologia%20Curitiba%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Odonto Kennedy Centro Odontolgico</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Odonto Kennedy Centro Odontológico</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Odonto Kennedy. 41 99595-1636. contato@odontokennedy.com.br. Instagram.Odontologia. Curitiba. Mude d...</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://odontokennedy.com.br/</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>41 99595-1636</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>554199595163600</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Odonto%20Kennedy%20Centro%20Odontolgico%20curitiba</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odonto Kennedy Centro Odontolgico aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odonto Kennedy Centro Odontolgico?</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>https://wa.me/554199595163600?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odonto%20Kennedy%20Centro%20Odontolgico%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>https://wa.me/554199595163600?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odonto%20Kennedy%20Centro%20Odontolgico%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Centro Odontolgico Fazendinha</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Centro Odontológico Fazendinha</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Curitiba</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Odontologia. Curitiba. Mude de vida. Conquiste um novo sorriso.Agende a sua consulta! Rua Carlos Kle...</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://odontologiafazendinha.com.br/</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>41 99595-1636</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>554199595163600</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Centro%20Odontolgico%20Fazendinha%20curitiba</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Centro Odontolgico Fazendinha aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Centro Odontolgico Fazendinha?</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>https://wa.me/554199595163600?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Centro%20Odontolgico%20Fazendinha%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>https://wa.me/554199595163600?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Centro%20Odontolgico%20Fazendinha%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20melhores%20barbeiros%20perto%20de%20mim%3F</t>
         </is>
       </c>
     </row>

--- a/leads_odontologia_curitiba.xlsx
+++ b/leads_odontologia_curitiba.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,12 +565,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CNPJ: 46.364.200/0001-24</t>
+          <t>Oral Unic Odontologia Curitiba LTDA CNPJ CURI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CNPJ: 46.364.200/0001-24 - Dental Design Curitiba Odontologia...</t>
+          <t>Oral Unic Odontologia Curitiba LTDA · CNPJ · CURITIBA/PR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>O CNPJ da empresa Dental Design Curitiba Odontologia Ltda (Dental Design Curitiba) é 46.364.200/0001...</t>
+          <t>Empresa ativa desde 2017 em CURITIBA/PR. Atividade: Atividade odontológica. Veja endereço, sócios, C...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,28 +595,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.nacionalconsultas.com.br/cnpj/dental-design-curitiba-odontologia-ltda-46364200000124</t>
+          <t>https://cnpjaberto.com.br/cnpj/28274955000156</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(41) 9851-2345</t>
+          <t>(28) 2749-5500</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>554198512345</t>
+          <t>552827495500</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/CNPJ%3A%2046.364.200/0001-24%20curitiba</t>
+          <t>https://www.google.com/maps/search/Oral%20Unic%20Odontologia%20Curitiba%20LTDA%20CNPJ%20CURI%20curitiba</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da CNPJ: 46.364.200/0001-24 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Oral Unic Odontologia Curitiba LTDA CNPJ CURI aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -626,29 +626,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a CNPJ: 46.364.200/0001-24?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Oral Unic Odontologia Curitiba LTDA CNPJ CURI?</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://wa.me/554198512345?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%3A%2046.364.200/0001-24%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/552827495500?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Oral%20Unic%20Odontologia%20Curitiba%20LTDA%20CNPJ%20CURI%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://wa.me/554198512345?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%3A%2046.364.200/0001-24%3F</t>
+          <t>https://wa.me/552827495500?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Oral%20Unic%20Odontologia%20Curitiba%20LTDA%20CNPJ%20CURI%3F</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Odontologia</t>
+          <t>CNPJ: 58.524.532/0001-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Odontologia em Curitiba | Murano Odontologia (41) 3253-1907 ...</t>
+          <t>CNPJ: 58.524.532/0001-08 - Tres Odontologia Curitiba Ltda...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A Clínica Murano Odontologia de Referência dá bons motivos para você ter um sorriso bonito e saudáve...</t>
+          <t>O CNPJ da empresa Tres Odontologia Curitiba Ltda é 58.524.532/0001-08. Com sede em CURITIBA, PR, pos...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -673,28 +673,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://muranoodontologia.com.br/</t>
+          <t>https://www.nacionalconsultas.com.br/cnpj/tres-odontologia-curitiba-ltda-58524532000108</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(41) 3253-1907</t>
+          <t>(02) 5581-5700</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>554132531907</t>
+          <t>550255815700</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/CNPJ%3A%2058.524.532/0001-08%20curitiba</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da CNPJ: 58.524.532/0001-08 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -704,29 +704,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a CNPJ: 58.524.532/0001-08?</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://wa.me/554132531907?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/550255815700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%3A%2058.524.532/0001-08%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://wa.me/554132531907?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%3F</t>
+          <t>https://wa.me/550255815700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%3A%2058.524.532/0001-08%3F</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Odontologia</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Curitiba - Centro - PR - Mappi Odontologia</t>
+          <t>Odontologia em Curitiba | Murano Odontologia (41) 3253-1907 ...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Conheça a unidade da Mappi no centro de Curitiba/PR e agende a sua avaliação agora mesmo para conqui...</t>
+          <t>A Clínica Murano Odontologia de Referência dá bons motivos para você ter um sorriso bonito e saudáve...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -751,28 +751,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://mappiodontologia.com.br/curitiba-centro-pr/</t>
+          <t>https://muranoodontologia.com.br/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(41) 9876-2903</t>
+          <t>(41) 3253-1907</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>554198762903</t>
+          <t>554132531907</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -782,29 +782,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odontologia?</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://wa.me/554198762903?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554132531907?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://wa.me/554198762903?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Curitiba%3F</t>
+          <t>https://wa.me/554132531907?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Encontrar seu smartphone</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Encontrar seu smartphone</t>
+          <t>Curitiba - Centro - PR - Mappi Odontologia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,34 +819,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Configurações da Conta do Google. Ajuda. Fazer login....</t>
+          <t>Conheça a unidade da Mappi no centro de Curitiba/PR e agende a sua avaliação agora mesmo para conqui...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://mappiodontologia.com.br/curitiba-centro-pr/</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(41) 9876-2903</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>554198762903</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Encontrar%20seu%20smartphone%20curitiba</t>
+          <t>https://www.google.com/maps/search/Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Encontrar seu smartphone aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -856,29 +860,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Encontrar seu smartphone?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Curitiba?</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Encontrar%20seu%20smartphone%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554198762903?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Encontrar%20seu%20smartphone%3F</t>
+          <t>https://wa.me/554198762903?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OpenGuessr</t>
+          <t>Dra.Keslen_Geffer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OpenGuessr - Error</t>
+          <t>Dra.Keslen_Geffer | Instagram | Linktree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -893,34 +897,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Openguessr - guess the country based off Google maps....</t>
+          <t>@Dra.Keslen_Geffer. Odontologia de excelência em Curitiba. Google Maps - 5.0. Agende sua Consulta. I...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://openguessr.com/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(41) 3252-1119</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>554132521119</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/OpenGuessr%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dra.Keslen_Geffer%20curitiba</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da OpenGuessr aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dra.Keslen_Geffer aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -930,29 +938,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a OpenGuessr?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dra.Keslen_Geffer?</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OpenGuessr%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554132521119?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra.Keslen_Geffer%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OpenGuessr%3F</t>
+          <t>https://wa.me/554132521119?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra.Keslen_Geffer%3F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Guess Where You Are</t>
+          <t>Encontrar seu smartphone</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guess Where You Are - Free GeoGuessr Alternative</t>
+          <t>Encontrar seu smartphone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -967,17 +975,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>community World (upload your map files to the Google doc)....</t>
+          <t>Configurações da Conta do Google. Ajuda. Fazer login....</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://guesswhereyouare.com/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -988,13 +996,13 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Guess%20Where%20You%20Are%20curitiba</t>
+          <t>https://www.google.com/maps/search/Encontrar%20seu%20smartphone%20curitiba</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Guess Where You Are aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Encontrar seu smartphone aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1004,29 +1012,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Guess Where You Are?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Encontrar seu smartphone?</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Guess%20Where%20You%20Are%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Encontrar%20seu%20smartphone%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Guess%20Where%20You%20Are%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Encontrar%20seu%20smartphone%3F</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clnica Felpe Odontologia Curitiba</t>
+          <t>Link to instagram.com</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clínica Felpe Odontologia Curitiba</t>
+          <t>Link to instagram.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1041,38 +1049,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Whatsapp Felpe Odontologia.Clínica Ortodôntica Curitiba. ORTODONTIA. Mostre o seu melhor sorriso e c...</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.felpe.com.br/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>41997321</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5541997321</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Felpe%20Odontologia%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20curitiba</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Felpe Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Link to instagram.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1082,29 +1086,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Felpe Odontologia Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://wa.me/5541997321?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Felpe%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20instagram.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://wa.me/5541997321?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Felpe%20Odontologia%20Curitiba%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20instagram.com%3F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UpClin Odontologia Curitiba</t>
+          <t>Clnica Felpe Odontologia Curitiba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UpClin Odontologia Curitiba</t>
+          <t>Clínica Felpe Odontologia Curitiba</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1119,7 +1123,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odontologia Curitiba, Odontopediatria, Ortodontia, Cirurgia Buco-Maxilo, Dentista Clínico Geral.O ra...</t>
+          <t>Whatsapp Felpe Odontologia.Clínica Ortodôntica Curitiba. ORTODONTIA. Mostre o seu melhor sorriso e c...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1129,28 +1133,28 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.upclin.com/</t>
+          <t>https://www.felpe.com.br/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(41) 3095-9660</t>
+          <t>41997321</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>554130959660</t>
+          <t>5541997321</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/UpClin%20Odontologia%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnica%20Felpe%20Odontologia%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da UpClin Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica Felpe Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1160,29 +1164,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a UpClin Odontologia Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Felpe Odontologia Curitiba?</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://wa.me/554130959660?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20UpClin%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541997321?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Felpe%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://wa.me/554130959660?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20UpClin%20Odontologia%20Curitiba%3F</t>
+          <t>https://wa.me/5541997321?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Felpe%20Odontologia%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SV Odontologia • Tratamento Invisalign e Orto</t>
+          <t>UpClin Odontologia Curitiba</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SV Odontologia • Tratamento Invisalign e Ortodontia • Curitiba PR</t>
+          <t>UpClin Odontologia Curitiba</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1197,7 +1201,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A SV Odontologia está comprometida em oferecer aos seus pacientes o melhor tratamento ortodôntico po...</t>
+          <t>Odontologia Curitiba, Odontopediatria, Ortodontia, Cirurgia Buco-Maxilo, Dentista Clínico Geral.O ra...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1207,7 +1211,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.svodontologia.com.br/</t>
+          <t>https://www.upclin.com/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1218,13 +1222,13 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20curitiba</t>
+          <t>https://www.google.com/maps/search/UpClin%20Odontologia%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da SV Odontologia • Tratamento Invisalign e Orto aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da UpClin Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1234,29 +1238,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a SV Odontologia • Tratamento Invisalign e Orto?</t>
+Posso te mandar a prévia demonstrativa que fiz para a UpClin Odontologia Curitiba?</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20UpClin%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20UpClin%20Odontologia%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pinho Odontologia</t>
+          <t>SV Odontologia • Tratamento Invisalign e Orto</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pinho Odontologia | Curitiba - PR</t>
+          <t>SV Odontologia • Tratamento Invisalign e Ortodontia • Curitiba PR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1271,7 +1275,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Clínica odontológica em Curitiba. Especialistas em implantes, ortodontia, invisalign, odontopediatri...</t>
+          <t>A SV Odontologia está comprometida em oferecer aos seus pacientes o melhor tratamento ortodôntico po...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1281,28 +1285,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://drpinho.com.br/</t>
+          <t>https://www.svodontologia.com.br/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(41) 3342-2121</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>554133422121</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Pinho%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20curitiba</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Pinho Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da SV Odontologia • Tratamento Invisalign e Orto aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1312,29 +1312,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Pinho Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a SV Odontologia • Tratamento Invisalign e Orto?</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://wa.me/554133422121?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Pinho%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://wa.me/554133422121?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Pinho%20Odontologia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20SV%20Odontologia%20%E2%80%A2%20Tratamento%20Invisalign%20e%20Orto%3F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dental Esthetic Center / odontologia curitiba</t>
+          <t>Pinho Odontologia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dental Esthetic Center / odontologia curitiba - YouTube</t>
+          <t>Pinho Odontologia | Curitiba - PR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1349,38 +1349,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vídeos produzidos pela Dental Esthetic Center by Rogério Marcondes sobre Odontologia Estética, proce...</t>
+          <t>Clínica odontológica em Curitiba. Especialistas em implantes, ortodontia, invisalign, odontopediatri...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://drpinho.com.br/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(41) 99280-3875</t>
+          <t>(41) 3342-2121</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5541992803875</t>
+          <t>554133422121</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Pinho%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dental Esthetic Center / odontologia curitiba aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Pinho Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1390,29 +1390,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dental Esthetic Center / odontologia curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Pinho Odontologia?</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://wa.me/5541992803875?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554133422121?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Pinho%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://wa.me/5541992803875?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%3F</t>
+          <t>https://wa.me/554133422121?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Pinho%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cury Clnica Odontolgica</t>
+          <t>Dental Esthetic Center / odontologia curitiba</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cury Clínica Odontológica</t>
+          <t>Dental Esthetic Center / odontologia curitiba - YouTube</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,34 +1427,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Clínica odontológica em Curitiba com espaço amplo e moderno, projetado para a oferecer toda a estrut...</t>
+          <t>Vídeos produzidos pela Dental Esthetic Center by Rogério Marcondes sobre Odontologia Estética, proce...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://ortodontiacuritiba.com.br/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(41) 99280-3875</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5541992803875</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Cury%20Clnica%20Odontolgica%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Cury Clnica Odontolgica aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dental Esthetic Center / odontologia curitiba aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1464,29 +1468,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Cury Clnica Odontolgica?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dental Esthetic Center / odontologia curitiba?</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Cury%20Clnica%20Odontolgica%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541992803875?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Cury%20Clnica%20Odontolgica%3F</t>
+          <t>https://wa.me/5541992803875?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dental%20Esthetic%20Center%20/%20odontologia%20curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Odonto Pio XII</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Odonto Pio XII - Seu dentista 24h em Curitiba</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,17 +1505,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Há mais de 40 anos no mercado, o Centro Odontológico Pio XII tornou-se referência na área odontológi...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.odontopioxii.com.br/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1522,13 +1526,13 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20curitiba</t>
+          <t>https://www.google.com/maps/search/Odonto%20Pio%20XII%20curitiba</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to instagram.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Odonto Pio XII aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1538,29 +1542,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odonto Pio XII?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20instagram.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odonto%20Pio%20XII%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20instagram.com%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odonto%20Pio%20XII%3F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Clnica Odontolgica</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Clínica Odontológica em Curitiba | WhatsApp: 41 98868-8164</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,34 +1579,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Clínica odontológica em Curitiba, moderna e completa para acolher toda a família. Odontopediatria, O...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.anaarantesodonto.com.br/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(41) 98868-8164</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5541988688164</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnica%20Odontolgica%20curitiba</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to facebook.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Clnica Odontolgica aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1612,29 +1620,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Odontolgica?</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988688164?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Odontolgica%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
+          <t>https://wa.me/5541988688164?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Odontolgica%3F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Clnicas</t>
+          <t>Instituto Odontolgico Edson Coser</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clínicas em Curitiba de Odontologia | Doctuo</t>
+          <t>Instituto Odontológico Edson Coser - Referência em Curitiba</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1649,7 +1657,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Clínicas de Odontologia em Curitiba.Rua Eunice Bettini Bartoszeck , 1151, Curitiba, Paraná. Uniodont...</t>
+          <t>As consultas podem ser agendadas diretamente pelo nosso site, via WhatsApp ou ligando para nossa clí...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1659,28 +1667,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.doctuo.com.br/centros-medicos/odontologia/curitiba</t>
+          <t>https://institutocoser.com.br/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(34) 3411-4813</t>
+          <t>(41) 98444-8862</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>553434114813</t>
+          <t>5541984448862</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnicas%20curitiba</t>
+          <t>https://www.google.com/maps/search/Instituto%20Odontolgico%20Edson%20Coser%20curitiba</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnicas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Instituto Odontolgico Edson Coser aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1690,29 +1698,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnicas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Instituto Odontolgico Edson Coser?</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://wa.me/553434114813?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnicas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541984448862?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Instituto%20Odontolgico%20Edson%20Coser%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://wa.me/553434114813?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnicas%3F</t>
+          <t>https://wa.me/5541984448862?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Instituto%20Odontolgico%20Edson%20Coser%3F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Centro Clinico Vidaclin Odontologia, Curitiba</t>
+          <t>ODONTOLOGIA COSTA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centro Clinico Vidaclin Odontologia, Curitiba — R. Urbâno Lopes..</t>
+          <t>ODONTOLOGIA COSTA - implantes dentarios Curitiba</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1727,7 +1735,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Centro Clinico Vidaclin Odontologia, endereço — R. Urbâno Lopes, 89 - Cristo Rei, Curitiba - PR, 800...</t>
+          <t>Bem-vindo a Odontologia Costa ! Atuamos desde 2005 no mesmo local (consultório próprio), no Centro d...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1737,28 +1745,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://br.polomap.com/curitiba/32560</t>
+          <t>https://www.odontologiacosta.com/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(41) 3362-7654</t>
+          <t>(41) 3322-9504</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>554133627654</t>
+          <t>554133229504</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Centro%20Clinico%20Vidaclin%20Odontologia%2C%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/ODONTOLOGIA%20COSTA%20curitiba</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Centro Clinico Vidaclin Odontologia, Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da ODONTOLOGIA COSTA aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1768,29 +1776,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Centro Clinico Vidaclin Odontologia, Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a ODONTOLOGIA COSTA?</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://wa.me/554133627654?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Centro%20Clinico%20Vidaclin%20Odontologia%2C%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554133229504?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20ODONTOLOGIA%20COSTA%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://wa.me/554133627654?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Centro%20Clinico%20Vidaclin%20Odontologia%2C%20Curitiba%3F</t>
+          <t>https://wa.me/554133229504?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20ODONTOLOGIA%20COSTA%3F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Clnica odontolgica de Curitiba</t>
+          <t>Fujikawa Odontologia Dentista</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Clínica odontológica de Curitiba - Odontologia Curitiba, PR</t>
+          <t>Fujikawa Odontologia Dentista em Curitiba</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1805,7 +1813,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Odontologia &amp; Harmonização facial, Curitiba. (41) 4101-3337.Conheça a Clínica Odontológica. Localiza...</t>
+          <t>A prótese dentária (ou prótese dental) é a área da Odontologia destinada a lidar com a reposição de ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1815,28 +1823,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://taiatellaodontologia.com.br/clinica-odontologica-odontologia-curitiba.html</t>
+          <t>https://fujikawaodontologia.com.br/</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(41) 4101-3337</t>
+          <t>(41) 98825-8833</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>554141013337</t>
+          <t>5541988258833</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20odontolgica%20de%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Fujikawa%20Odontologia%20Dentista%20curitiba</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica odontolgica de Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Fujikawa Odontologia Dentista aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1846,29 +1854,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica odontolgica de Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Fujikawa Odontologia Dentista?</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://wa.me/554141013337?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20odontolgica%20de%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988258833?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Fujikawa%20Odontologia%20Dentista%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://wa.me/554141013337?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20odontolgica%20de%20Curitiba%3F</t>
+          <t>https://wa.me/5541988258833?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Fujikawa%20Odontologia%20Dentista%3F</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>105 Odontologia</t>
+          <t>Dentista</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>105 Odontologia - Curitiba - PR - Somos Popular</t>
+          <t>Dentista em Curitiba - Boqueirão | Centro Odontológico Mangini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1883,38 +1891,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>105 Odontologia - Curitiba - PR. Clínica Popular com preços muito mais acessíveis.Endereço: Avenida ...</t>
+          <t>No Centro Odontológico Mangini você conta com uma equipe especializada, equipamentos e técnicas mode...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR (ERRO 404) 🚨</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.somospopular.com.br/hospitais-e-ambulatorios/105-odontologia-curitiba-pr/</t>
+          <t>https://manginiodontologia.com.br/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>41301027</t>
+          <t>(41) 99257-8253</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5541301027</t>
+          <t>5541992578253</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/105%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dentista%20curitiba</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 105 Odontologia aí em Curitiba no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Dentista aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1924,29 +1932,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 105 Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista?</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://wa.me/5541301027?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20105%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541992578253?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://wa.me/5541301027?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20105%20Odontologia%3F</t>
+          <t>https://wa.me/5541992578253?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%3F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mandic</t>
+          <t>Consultrio odontolgico</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mandic - Curitiba | São Leopoldo Mandic</t>
+          <t>Consultório odontológico em Curitiba | Actual Consultório ...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1961,7 +1969,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>A Unidade de Curitiba da Faculdade São Leopoldo Mandic existe desde 2003, e segue deixando sua marca...</t>
+          <t>No actual consultório odontológico, cuidamos do seu sorriso com atenção e carinho para promover saúd...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1971,28 +1979,28 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://slmandic.edu.br/unidade/curitiba</t>
+          <t>https://xn--actualconsultrioodontologico-xzc.com/</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(09) 2457-2000</t>
+          <t>(19) 4108-2486</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>550924572000</t>
+          <t>551941082486</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Mandic%20curitiba</t>
+          <t>https://www.google.com/maps/search/Consultrio%20odontolgico%20curitiba</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Mandic aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Consultrio odontolgico aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2002,29 +2010,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Mandic?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Consultrio odontolgico?</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://wa.me/550924572000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Mandic%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551941082486?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20odontolgico%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://wa.me/550924572000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Mandic%3F</t>
+          <t>https://wa.me/551941082486?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20odontolgico%3F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sorri Dente Odontologia</t>
+          <t>Cury Clnica Odontolgica</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sorri Dente Odontologia - Curitiba - PR - Consultório</t>
+          <t>Cury Clínica Odontológica</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2039,7 +2047,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sorri Dente Odontologia - Centro - Curitiba - PR - Saúde Bucal.Estabelecimento do Tipo: Consultório....</t>
+          <t>Clínica odontológica em Curitiba com espaço amplo e moderno, projetado para a oferecer toda a estrut...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2049,28 +2057,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cebes.com.br/sorri-dente-odontologia-1078542/</t>
+          <t>https://ortodontiacuritiba.com.br/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(41) 99976-7375</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5541999767375</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Sorri%20Dente%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Cury%20Clnica%20Odontolgica%20curitiba</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Sorri Dente Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Cury Clnica Odontolgica aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2080,29 +2084,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Sorri Dente Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Cury Clnica Odontolgica?</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://wa.me/5541999767375?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Sorri%20Dente%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Cury%20Clnica%20Odontolgica%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://wa.me/5541999767375?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Sorri%20Dente%20Odontologia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Cury%20Clnica%20Odontolgica%3F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Arch Odontologia</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arch Odontologia | Curitiba | Clínica Odontológica</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2117,38 +2121,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aqui na Arch Odontologia, você encontra os mais modernos tratamentos estéticos odontológicos: faceta...</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.archodontologia.com/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(41) 3022-2999</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>554130222999</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Arch%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20curitiba</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Arch Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Link to facebook.com aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2158,29 +2158,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Arch Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://wa.me/554130222999?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Arch%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://wa.me/554130222999?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Arch%20Odontologia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bittencourt Odontologia</t>
+          <t>Clnicas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bittencourt Odontologia | Dentistas em Curitiba | Paraná</t>
+          <t>Clínicas em Curitiba de Odontologia | Doctuo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bem-Vindo(a) à Bittencourt Odontologia. Atendimento Completo Para Toda Família! Temos uma equipe de ...</t>
+          <t>Clínicas de Odontologia em Curitiba.Rua Eunice Bettini Bartoszeck , 1151, Curitiba, Paraná. Uniodont...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2205,28 +2205,28 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.bittencourtodontologia.com.br/</t>
+          <t>https://www.doctuo.com.br/centros-medicos/odontologia/curitiba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(19) 3816-7455</t>
+          <t>(34) 3411-4813</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>551938167455</t>
+          <t>553434114813</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bittencourt%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnicas%20curitiba</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Bittencourt Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnicas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2236,29 +2236,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Bittencourt Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnicas?</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://wa.me/551938167455?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bittencourt%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/553434114813?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnicas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://wa.me/551938167455?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bittencourt%20Odontologia%3F</t>
+          <t>https://wa.me/553434114813?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnicas%3F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Citag Odontologia</t>
+          <t>Perfectta Odontologia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Citag Odontologia – O sorriso dos sonhos, pra você!</t>
+          <t>Perfectta Odontologia - Perfectta Odontologia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Diferenciais da Citag Odontologia. Entenda o porque somos referência na Odontologia em Curitiba! Pro...</t>
+          <t>Clínica odontológica em Curitiba.Cuidar do seu sorriso é a nossa especialidade. Na Perfectta Odontol...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2283,28 +2283,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://citagodontologia.com.br/</t>
+          <t>https://perfecttaodontologia.com.br/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(47) 1562-3100</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>554715623100</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Citag%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Perfectta%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Citag Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Perfectta Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2314,29 +2310,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Citag Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Perfectta Odontologia?</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://wa.me/554715623100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Citag%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Perfectta%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://wa.me/554715623100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Citag%20Odontologia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Perfectta%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dra. Izabela Taiatella</t>
+          <t>Implantes Dentrios e Prtese Protocolo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dra. Izabela Taiatella - Odontologia em CURITIBA</t>
+          <t>Implantes Dentários e Prótese Protocolo em Curitiba</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2351,7 +2347,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dra. Izabela Taiatella - Odontologia e Harmonização facial, Curitiba - Uma profissional altamente qu...</t>
+          <t>Clínica de Ortodontia e Implantodontia em Curitiba, Implantes e Aparelhos Dentários Transparentes e ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2361,7 +2357,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://taiatellaodontologia.com.br/</t>
+          <t>https://debocaaberta.com.br/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2372,13 +2368,13 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dra.%20Izabela%20Taiatella%20curitiba</t>
+          <t>https://www.google.com/maps/search/Implantes%20Dentrios%20e%20Prtese%20Protocolo%20curitiba</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dra. Izabela Taiatella aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Implantes Dentrios e Prtese Protocolo aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2388,29 +2384,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dra. Izabela Taiatella?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Implantes Dentrios e Prtese Protocolo?</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra.%20Izabela%20Taiatella%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Implantes%20Dentrios%20e%20Prtese%20Protocolo%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra.%20Izabela%20Taiatella%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Implantes%20Dentrios%20e%20Prtese%20Protocolo%3F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fujikawa Odontologia Dentista</t>
+          <t>10 melhores dentistas para Curitiba</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fujikawa Odontologia Dentista em Curitiba. Atendemos plano AMIL</t>
+          <t>10 melhores dentistas para Curitiba</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2425,7 +2421,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Entre em contato conosco por telefone, formulário de contato ou Whatsapp que retornaremos com priori...</t>
+          <t>80020-340 Curitiba. Mestre e Doutorando em Odontologia Clínica, especialista em tratamentos estético...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2435,28 +2431,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://fujikawaodontologia.com.br/</t>
+          <t>https://www.starofservice.com.br/dir/parana/curitiba/curitiba/servicos-dentarios</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(41) 98825-8833</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5541988258833</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Fujikawa%20Odontologia%20Dentista%20curitiba</t>
+          <t>https://www.google.com/maps/search/10%20melhores%20dentistas%20para%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Fujikawa Odontologia Dentista aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 10 melhores dentistas para Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2466,29 +2458,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Fujikawa Odontologia Dentista?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 10 melhores dentistas para Curitiba?</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988258833?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Fujikawa%20Odontologia%20Dentista%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20melhores%20dentistas%20para%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988258833?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Fujikawa%20Odontologia%20Dentista%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20melhores%20dentistas%20para%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Clinident</t>
+          <t>Dentistas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clinident | Clínica Odontológica em Curitiba desde 1968</t>
+          <t>Dentistas em Curitiba - PR: 2195 avaliados · 4.8 | DentMap</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2503,7 +2495,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Na Clinident, você encontra atendimento odontológico completo em Curitiba, com emergência, raio-X od...</t>
+          <t>2324 dentistas em Curitiba, PR em 27 bairros. Nota média 4.8. Veja WhatsApp e telefone, compare aval...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2513,24 +2505,28 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://clinident24h.com.br/</t>
+          <t>https://dentmap.com.br/dentistas/curitiba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(41) 99567-6216</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5541995676216</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clinident%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dentistas%20curitiba</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clinident aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dentistas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2540,29 +2536,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clinident?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentistas?</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clinident%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541995676216?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentistas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clinident%3F</t>
+          <t>https://wa.me/5541995676216?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentistas%3F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Clinident 24 Horas</t>
+          <t>Clnica odontolgica de Curitiba</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Clinident 24 Horas - Dentista 24 Horas em Curitiba | dentista ...</t>
+          <t>Clínica odontológica de Curitiba - Odontologia Curitiba, PR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2577,7 +2573,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fornecemos atendimento odontológico abrangente, com uma equipe preparada para oferecer o melhor serv...</t>
+          <t>Odontologia &amp; Harmonização facial, Curitiba. (41) 4101-3337.Conheça a Clínica Odontológica. Localiza...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2587,28 +2583,28 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://clinident24h.com.br/contato.html</t>
+          <t>https://taiatellaodontologia.com.br/clinica-odontologica-odontologia-curitiba.html</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(41) 3264-1984</t>
+          <t>(41) 4101-3337</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>554132641984</t>
+          <t>554141013337</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clinident%2024%20Horas%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clnica%20odontolgica%20de%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clinident 24 Horas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica odontolgica de Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2618,29 +2614,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clinident 24 Horas?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica odontolgica de Curitiba?</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://wa.me/554132641984?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clinident%2024%20Horas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554141013337?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20odontolgica%20de%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://wa.me/554132641984?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clinident%2024%20Horas%3F</t>
+          <t>https://wa.me/554141013337?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20odontolgica%20de%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Odonto Pio XII</t>
+          <t>10 MELHORES Clnicas Odontolgicas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Odonto Pio XII - Seu dentista 24h em Curitiba</t>
+          <t>10 MELHORES Clínicas Odontológicas em Curitiba, PR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2655,7 +2651,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Localizado no centro de Curitiba, região de fácil acesso para pacientes de todas as regiões da cidad...</t>
+          <t>10 MELHORES Clínicas Odontológicas em Curitiba, PR, encontre informações, telefones, endereços, mapa...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2665,7 +2661,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.odontopioxii.com.br/</t>
+          <t>https://www.guiatelefone.com/empresas/curitiba-pr/clinicas-medicos-e-terapias/clinicas-odontologicas</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2676,13 +2672,13 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odonto%20Pio%20XII%20curitiba</t>
+          <t>https://www.google.com/maps/search/10%20MELHORES%20Clnicas%20Odontolgicas%20curitiba</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odonto Pio XII aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 10 MELHORES Clnicas Odontolgicas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2692,29 +2688,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odonto Pio XII?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 10 MELHORES Clnicas Odontolgicas?</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odonto%20Pio%20XII%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2010%20MELHORES%20Clnicas%20Odontolgicas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odonto%20Pio%20XII%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2010%20MELHORES%20Clnicas%20Odontolgicas%3F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Egao Odontologia</t>
+          <t>Maxiclin Odontologia Curitiba</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Egao Odontologia - Dentista em Curitiba - PR</t>
+          <t>Maxiclin Odontologia Curitiba | Excelência em Odontologia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2729,7 +2725,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Com a chancela do Dr. Carlos Shiratori, a Egao Odontologia conta com mais de duas décadas de atendim...</t>
+          <t>A Maxiclin é uma clínica de odontologia em Curitiba que oferece atendimento odontológico interdiscip...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2739,28 +2735,28 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://egao.com.br/</t>
+          <t>https://www.maxiclin.com.br/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(41) 3257-1026</t>
+          <t>(41) 98519-4512</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>554132571026</t>
+          <t>5541985194512</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Egao%20Odontologia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Maxiclin%20Odontologia%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Egao Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Maxiclin Odontologia Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2770,29 +2766,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Egao Odontologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Maxiclin Odontologia Curitiba?</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://wa.me/554132571026?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Egao%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541985194512?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Maxiclin%20Odontologia%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://wa.me/554132571026?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Egao%20Odontologia%3F</t>
+          <t>https://wa.me/5541985194512?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Maxiclin%20Odontologia%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dentista Ortodontista Invisalign Curitiba</t>
+          <t>Egao Odontologia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dentista Ortodontista Invisalign Curitiba - Barusso</t>
+          <t>Egao Odontologia - Dentista em Curitiba - PR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2807,7 +2803,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Conheça alguns tratamentos Odontológicos Ortodontia Dentista Ortodontista. Aparelhos fixos e removív...</t>
+          <t>A Egao Odontologia é uma clínica odontológica multidisciplinar localizada no coração de Curitiba. Te...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2817,28 +2813,28 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://barussodontologia.com.br/</t>
+          <t>https://egao.com.br/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(41) 99128-7722</t>
+          <t>(41) 3257-1026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5541991287722</t>
+          <t>554132571026</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Dentista%20Ortodontista%20Invisalign%20Curitiba%20curitiba</t>
+          <t>https://www.google.com/maps/search/Egao%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Dentista Ortodontista Invisalign Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Egao Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2848,29 +2844,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Dentista Ortodontista Invisalign Curitiba?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Egao Odontologia?</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://wa.me/5541991287722?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20Ortodontista%20Invisalign%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554132571026?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Egao%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://wa.me/5541991287722?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20Ortodontista%20Invisalign%20Curitiba%3F</t>
+          <t>https://wa.me/554132571026?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Egao%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Odonto Kennedy Centro Odontolgico</t>
+          <t>Clinident</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Odonto Kennedy Centro Odontológico</t>
+          <t>Clinident | Clínica Odontológica em Curitiba desde 1968</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2885,7 +2881,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Odonto Kennedy. 41 99595-1636. contato@odontokennedy.com.br. Instagram.Odontologia. Curitiba. Mude d...</t>
+          <t>Está com dor ou precisa de atendimento odontológico? A Clinident atende diariamente das 08h à meia-n...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2895,28 +2891,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://odontokennedy.com.br/</t>
+          <t>https://clinident24h.com.br/</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(41) 99595-1636</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5541995951636</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Odonto%20Kennedy%20Centro%20Odontolgico%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clinident%20curitiba</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Odonto Kennedy Centro Odontolgico aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clinident aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2926,29 +2918,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Odonto Kennedy Centro Odontolgico?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clinident?</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://wa.me/5541995951636?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odonto%20Kennedy%20Centro%20Odontolgico%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clinident%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://wa.me/5541995951636?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odonto%20Kennedy%20Centro%20Odontolgico%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clinident%3F</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Barbearia</t>
+          <t>Bittencourt Odontologia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Barbearia em Curitiba - perto de mim - Cabeleireiro masculino ...</t>
+          <t>Bittencourt Odontologia | Dentistas em Curitiba | Paraná</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2963,7 +2955,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Um recurso incrível que você pode utilizar é o nosso mapa virtual, em que você pode encontrar todas ...</t>
+          <t>Bem-Vindo(a) à Bittencourt Odontologia. Atendimento Completo Para Toda Família! Temos uma equipe de ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2973,28 +2965,28 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://booksy.com/pt-br/s/barbearias/583853_curitiba</t>
+          <t>https://www.bittencourtodontologia.com.br/</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(41) 99861-8127</t>
+          <t>(19) 3816-7455</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5541998618127</t>
+          <t>551938167455</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Bittencourt%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Bittencourt Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3004,29 +2996,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Bittencourt Odontologia?</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://wa.me/5541998618127?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551938167455?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bittencourt%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://wa.me/5541998618127?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%3F</t>
+          <t>https://wa.me/551938167455?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bittencourt%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>barbearias</t>
+          <t>Unik Odontologia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>barbearias em Curitiba 2026 | OndeAbrir</t>
+          <t>Unik Odontologia – Clínica odontológica</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3041,7 +3033,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Panorama competitivo: barbearias em Curitiba. Curitiba tem 1.8M habitantes e um mercado de barbearia...</t>
+          <t>Entre em Contato Conosco. R. Paulo Setúbal, 3280 Hauer, Curitiba - PR. (41) 3408-5222. contato@uniko...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3051,24 +3043,28 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://ondeabrir.com/mercado/barbearia/curitiba</t>
+          <t>https://unikodontologia.com/</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(41) 3408-5222</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>554134085222</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/barbearias%20curitiba</t>
+          <t>https://www.google.com/maps/search/Unik%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Unik Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3078,29 +3074,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a barbearias?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Unik Odontologia?</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554134085222?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Unik%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20barbearias%3F</t>
+          <t>https://wa.me/554134085222?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Unik%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Barbearia Clube</t>
+          <t>Dra. Izabela Taiatella</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Barbearia Clube | Tradição e Excelência em Curitiba (Mercês)</t>
+          <t>Dra. Izabela Taiatella - Odontologia em CURITIBA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3115,7 +3111,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>A barbearia clássica preferida de Curitiba. Barbearia Clube: Barba na navalha, cortes visagistas, Di...</t>
+          <t>Dra. Izabela Taiatella - Odontologia e Harmonização facial, Curitiba - Uma profissional altamente qu...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3125,28 +3121,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://barbeariaclube.com.br/</t>
+          <t>https://taiatellaodontologia.com.br/</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(41) 3014-9413</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>554130149413</t>
-        </is>
-      </c>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Clube%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dra.%20Izabela%20Taiatella%20curitiba</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Clube aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Dra. Izabela Taiatella aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3156,29 +3148,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Clube?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dra. Izabela Taiatella?</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://wa.me/554130149413?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Clube%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dra.%20Izabela%20Taiatella%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://wa.me/554130149413?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Clube%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dra.%20Izabela%20Taiatella%3F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CNPJ 53.441.822/0001-74</t>
+          <t>Citag Odontologia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CNPJ 53.441.822/0001-74 - barbearia curitiba ltda | CNPJ go!</t>
+          <t>Citag Odontologia – O sorriso dos sonhos, pra você!</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3193,7 +3185,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Enriqueça empresas com Google Maps, Instagram, LinkedIn e mais. A IA gera pitchs personalizados para...</t>
+          <t>Diferenciais da Citag Odontologia. Entenda o porque somos referência na Odontologia em Curitiba! Pro...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3203,24 +3195,28 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cnpjgo.com.br/cnpj/53441822000174</t>
+          <t>https://citagodontologia.com.br/</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(47) 1562-3100</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>554715623100</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/CNPJ%2053.441.822/0001-74%20curitiba</t>
+          <t>https://www.google.com/maps/search/Citag%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da CNPJ 53.441.822/0001-74 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Citag Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3230,29 +3226,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a CNPJ 53.441.822/0001-74?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Citag Odontologia?</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%2053.441.822/0001-74%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554715623100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Citag%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%2053.441.822/0001-74%3F</t>
+          <t>https://wa.me/554715623100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Citag%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Victor Hugo Barbeiro da Lenno Barbearia</t>
+          <t>Clinident 24 Horas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Victor Hugo Barbeiro da Lenno Barbearia - Curitiba 2017 - YouTube</t>
+          <t>Clinident 24 Horas - Dentista 24 Horas em Curitiba | dentista ...</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3267,38 +3263,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>© 2025 Google LLC....</t>
+          <t>Fornecemos atendimento odontológico abrangente, com uma equipe preparada para oferecer o melhor serv...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://clinident24h.com.br/contato.html</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(42) 2590-7400</t>
+          <t>(41) 3264-1984</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>554225907400</t>
+          <t>554132641984</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20curitiba</t>
+          <t>https://www.google.com/maps/search/Clinident%2024%20Horas%20curitiba</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Victor Hugo Barbeiro da Lenno Barbearia aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Clinident 24 Horas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3308,29 +3304,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Victor Hugo Barbeiro da Lenno Barbearia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clinident 24 Horas?</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://wa.me/554225907400?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554132641984?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clinident%2024%20Horas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://wa.me/554225907400?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%3F</t>
+          <t>https://wa.me/554132641984?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clinident%2024%20Horas%3F</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Barbearia Saint Germain</t>
+          <t>Arch Odontologia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Barbearia Saint Germain em Curitiba, PR | MestreGeo</t>
+          <t>Arch Odontologia | Curitiba | Clínica Odontológica</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3345,7 +3341,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Informações completas da organização BARBEARIA SAINT GERMAIN LTDA em Curitiba, Paraná. CNPJ: 36.748....</t>
+          <t>Aqui na Arch Odontologia, você encontra os mais modernos tratamentos estéticos odontológicos: faceta...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3355,28 +3351,28 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://mestregeo.com.br/cnpj/pr/curitiba/barbearia-saint-germain-36748126000196</t>
+          <t>https://www.archodontologia.com/</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(41) 99894-4124</t>
+          <t>(41) 3022-2999</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5541998944124</t>
+          <t>554130222999</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Saint%20Germain%20curitiba</t>
+          <t>https://www.google.com/maps/search/Arch%20Odontologia%20curitiba</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Saint Germain aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Arch Odontologia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3386,29 +3382,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Saint Germain?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Arch Odontologia?</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://wa.me/5541998944124?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Saint%20Germain%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554130222999?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Arch%20Odontologia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://wa.me/5541998944124?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Saint%20Germain%3F</t>
+          <t>https://wa.me/554130222999?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Arch%20Odontologia%3F</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Barbearias / Barbeiros</t>
+          <t>Dentista Ortodontista Invisalign Curitiba</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Barbearias / Barbeiros em Curitiba, PR — WhatsApp</t>
+          <t>Dentista Ortodontista Invisalign Curitiba - Barusso</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3423,17 +3419,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Veja os barbeiros mais bem avaliados em Curitiba, PR. Corte masculino, barba, degradê, navalhado e t...</t>
+          <t>Conheça alguns tratamentos Odontológicos Ortodontia Dentista Ortodontista. Aparelhos fixos e removív...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://barussodontologia.com.br/</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3444,13 +3440,13 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearias%20/%20Barbeiros%20curitiba</t>
+          <t>https://www.google.com/maps/search/Dentista%20Ortodontista%20Invisalign%20Curitiba%20curitiba</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearias / Barbeiros aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Dentista Ortodontista Invisalign Curitiba aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3460,29 +3456,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearias / Barbeiros?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Dentista Ortodontista Invisalign Curitiba?</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearias%20/%20Barbeiros%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Dentista%20Ortodontista%20Invisalign%20Curitiba%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearias%20/%20Barbeiros%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Dentista%20Ortodontista%20Invisalign%20Curitiba%3F</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15 Melhores Barbearias no gua Verde</t>
+          <t>Odonto Kennedy Centro Odontolgico</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15 Melhores Barbearias no Água Verde em Curitiba — Guia... | Bear</t>
+          <t>Odonto Kennedy Centro Odontológico</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3497,7 +3493,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8. Kennedy Barbearia | Barbearia Água Verde Curitiba. 9. Mr. Capelli Barber shop.Destacam-se a Barbe...</t>
+          <t>Odonto Kennedy. 41 99595-1636. contato@odontokennedy.com.br. Instagram.Odontologia. Curitiba. Mude d...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3507,24 +3503,28 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://blog.beard.com.br/barbearias-no-agua-verde-curitiba/</t>
+          <t>https://odontokennedy.com.br/</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(41) 99595-1636</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5541995951636</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/15%20Melhores%20Barbearias%20no%20gua%20Verde%20curitiba</t>
+          <t>https://www.google.com/maps/search/Odonto%20Kennedy%20Centro%20Odontolgico%20curitiba</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 15 Melhores Barbearias no gua Verde aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Odonto Kennedy Centro Odontolgico aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3534,29 +3534,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 15 Melhores Barbearias no gua Verde?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Odonto Kennedy Centro Odontolgico?</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2015%20Melhores%20Barbearias%20no%20gua%20Verde%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541995951636?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Odonto%20Kennedy%20Centro%20Odontolgico%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2015%20Melhores%20Barbearias%20no%20gua%20Verde%3F</t>
+          <t>https://wa.me/5541995951636?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Odonto%20Kennedy%20Centro%20Odontolgico%3F</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CNPJ: 18.553.536/0001-08</t>
+          <t>Barbearia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CNPJ: 18.553.536/0001-08 - Barbearia Curitiba Ltda - Nacional...</t>
+          <t>Barbearia em Curitiba - perto de mim - Cabeleireiro masculino ...</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O CNPJ da empresa Barbearia Curitiba Ltda (Barbearia Clube) é 18.553.536/0001-08. Com sede em CURITI...</t>
+          <t>Um recurso incrível que você pode utilizar é o nosso mapa virtual, em que você pode encontrar todas ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3581,28 +3581,28 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.nacionalconsultas.com.br/cnpj/barbearia-curitiba-ltda-18553536000108</t>
+          <t>https://booksy.com/pt-br/s/barbearias/583853_curitiba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(02) 5581-5700</t>
+          <t>(41) 99861-8127</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>550255815700</t>
+          <t>5541998618127</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/CNPJ%3A%2018.553.536/0001-08%20curitiba</t>
+          <t>https://www.google.com/maps/search/Barbearia%20curitiba</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da CNPJ: 18.553.536/0001-08 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3612,29 +3612,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a CNPJ: 18.553.536/0001-08?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia?</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://wa.me/550255815700?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%3A%2018.553.536/0001-08%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541998618127?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://wa.me/550255815700?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%3A%2018.553.536/0001-08%3F</t>
+          <t>https://wa.me/5541998618127?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%3F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CNPJ: 37.393.890/0001-59</t>
+          <t>Os melhores barbeiros perto de mim</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CNPJ: 37.393.890/0001-59 - La Mafia Social Club Barbearia Curitib</t>
+          <t xml:space="preserve">Os melhores barbeiros perto de mim em Curitiba - FreshaBarbearia </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>O CNPJ da empresa La Mafia Social Club Barbearia Curitiba Ltda. é 37.393.890/0001-59. Com sede em CU...</t>
+          <t>Agendar online com os melhores Barbeiros perto de você em Curitiba. Excelentes ofertas e descontos! ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3659,24 +3659,28 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.informecadastral.com.br/cnpj/la-mafia-social-club-barbearia-curitiba-ltda-37393890000159</t>
+          <t>https://www.fresha.com/lp/pt/bt/barbearias/br-curitiba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(CU) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>34028872</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5534028872</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/CNPJ%3A%2037.393.890/0001-59%20curitiba</t>
+          <t>https://www.google.com/maps/search/Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da CNPJ: 37.393.890/0001-59 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Os melhores barbeiros perto de mim aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3686,29 +3690,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a CNPJ: 37.393.890/0001-59?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Os melhores barbeiros perto de mim?</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%3A%2037.393.890/0001-59%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5534028872?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20melhores%20barbeiros%20perto%20de%20mim%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%3A%2037.393.890/0001-59%3F</t>
+          <t>https://wa.me/5534028872?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20melhores%20barbeiros%20perto%20de%20mim%3F</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Os melhores barbeiros perto de mim</t>
+          <t>Barbearia Saint Germain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os melhores barbeiros perto de mim em Curitiba - FreshaBarbearia </t>
+          <t>Barbearia Saint Germain | Curitiba</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3723,7 +3727,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Agendar online com os melhores Barbeiros perto de você em Curitiba. Excelentes ofertas e descontos! ...</t>
+          <t>Para quem busca uma barbearia em Curitiba que combine sofisticação, qualidade e atendimento atencios...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3733,44 +3737,808 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.fresha.com/lp/pt/bt/barbearias/br-curitiba</t>
+          <t>https://www.barbeariasg.com/</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
+          <t>(41) 99894-4124</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5541998944124</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Barbearia%20Saint%20Germain%20curitiba</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Barbearia Saint Germain aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Saint Germain?</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541998944124?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Saint%20Germain%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541998944124?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Saint%20Germain%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>15 Melhores Barbearias no Rebouas</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15 Melhores Barbearias no Rebouças em Curitiba — Guia 2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Neste guia reunimos as 15 melhores barbearias no Rebouças, selecionadas com base nas avaliações reai...</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://blog.beard.com.br/barbearias-no-reboucas-curitiba/</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>(CU) 98877-6655</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Os%20melhores%20barbeiros%20perto%20de%20mim%20curitiba</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Os melhores barbeiros perto de mim aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Os melhores barbeiros perto de mim?</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20melhores%20barbeiros%20perto%20de%20mim%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20melhores%20barbeiros%20perto%20de%20mim%3F</t>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/15%20Melhores%20Barbearias%20no%20Rebouas%20curitiba</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da 15 Melhores Barbearias no Rebouas aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a 15 Melhores Barbearias no Rebouas?</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2015%20Melhores%20Barbearias%20no%20Rebouas%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2015%20Melhores%20Barbearias%20no%20Rebouas%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>barbearias</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>barbearias em Curitiba 2026 | OndeAbrir</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Panorama competitivo: barbearias em Curitiba. Curitiba tem 1.8M habitantes e um mercado de barbearia...</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://ondeabrir.com/mercado/barbearia/curitiba</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/barbearias%20curitiba</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a barbearias?</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20barbearias%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Barbers In Barbearia</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Barbers In Barbearia - Curitiba - Faça Agendamentos Online - Preç</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Confira Barbers In Barbearia em Curitiba - explore preços, avaliações e faça agendamentos online 24 ...</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://booksy.com/pt-br/99716_barbers-in-barbearia_barbearias_583853_curitiba</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(41) 3598-9540</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>554135989540</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Barbers%20In%20Barbearia%20curitiba</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Barbers In Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Barbers In Barbearia?</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://wa.me/554135989540?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbers%20In%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://wa.me/554135989540?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbers%20In%20Barbearia%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Melhores Servios de Barbearias</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Melhores Serviços de Barbearias em Curitiba, PR | GuiaFix</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Descubra a Soul Barbearia, localizada no Shopping Estação de Curitiba. Nossa barbearia oferece um am...</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://guiafix.com.br/curitiba-pr/barbearias</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(41) 99894-4124</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5541998944124</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Melhores%20Servios%20de%20Barbearias%20curitiba</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Melhores Servios de Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Melhores Servios de Barbearias?</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541998944124?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Melhores%20Servios%20de%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541998944124?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Melhores%20Servios%20de%20Barbearias%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Barbearia Clube</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Barbearia Clube | Tradição e Excelência em Curitiba (Mercês)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>A barbearia clássica preferida de Curitiba. Barbearia Clube: Barba na navalha, cortes visagistas, Di...</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://barbeariaclube.com.br/</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(41) 3014-9413</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>554130149413</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Barbearia%20Clube%20curitiba</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Barbearia Clube aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Clube?</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://wa.me/554130149413?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Clube%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://wa.me/554130149413?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Clube%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AutoRank para Barbearias</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AutoRank para Barbearias em Curitiba | Seu Negócio na Primeira...</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Barbearias em Curitiba. Coloque sua barbearia na primeira página do Google e atraia clientes buscand...</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.autorank.com.br/barbearia/curitiba</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/AutoRank%20para%20Barbearias%20curitiba</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da AutoRank para Barbearias aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a AutoRank para Barbearias?</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20AutoRank%20para%20Barbearias%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20AutoRank%20para%20Barbearias%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shelby Barbearia</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Shelby Barbearia - (41) 98475-3472 BARBEARIA EM CURITIBA...</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Há 6 anos, a Shelby Barbearia vem construindo uma história de dedicação, estilo e excelência em Curi...</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://barbeariashelby.com.br/sobre-nos/</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(41) 98475-3472</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5541984753472</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Shelby%20Barbearia%20curitiba</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Shelby Barbearia aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Shelby Barbearia?</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541984753472?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Shelby%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541984753472?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Shelby%20Barbearia%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Barbearia John Six</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Barbearia John Six - Bigorrilho em Curitiba - PR | Locais do Bras</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Barbearia John Six - Bigorrilho atua no ramo de Barbearia, horário de funcionamento quarta a quinta-...</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.locaisdobrasil.com.br/encontre/barbearia/curitiba-pr/barbearia-john-six-bigorrilho/61cf4338c76c53fe0914d004</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(41) 1111-1111</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>554111111111</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Barbearia%20John%20Six%20curitiba</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Barbearia John Six aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia John Six?</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://wa.me/554111111111?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20John%20Six%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>https://wa.me/554111111111?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20John%20Six%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CNPJ 53.441.822/0001-74</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CNPJ 53.441.822/0001-74 - barbearia curitiba ltda | CNPJ go!</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Enriqueça empresas com Google Maps, Instagram, LinkedIn e mais. A IA gera pitchs personalizados para...</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://cnpjgo.com.br/cnpj/53441822000174</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/CNPJ%2053.441.822/0001-74%20curitiba</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da CNPJ 53.441.822/0001-74 aí em Curitiba no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a CNPJ 53.441.822/0001-74?</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%2053.441.822/0001-74%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%2053.441.822/0001-74%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Victor Hugo Barbeiro da Lenno Barbearia</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Victor Hugo Barbeiro da Lenno Barbearia - Curitiba 2017 - YouTube</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>© 2025 Google LLC....</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sem Site Cadastrado</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(CU) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20curitiba</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Victor Hugo Barbeiro da Lenno Barbearia aí em Curitiba no Google e vi que vocês ainda não têm um site próprio para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Victor Hugo Barbeiro da Lenno Barbearia?</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%20a%C3%AD%20em%20Curitiba%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Victor%20Hugo%20Barbeiro%20da%20Lenno%20Barbearia%3F</t>
         </is>
       </c>
     </row>

--- a/leads_odontologia_curitiba.xlsx
+++ b/leads_odontologia_curitiba.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OralClick Odontologia Curitiba 4.9 (4) Clnico</t>
+          <t>Oralclick Odontologia Curitiba 4.9 (4) C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Oral Unic Odontologia Curitiba LTDA CNPJ CURI</t>
+          <t>Oral Unic Odontologia Curitiba Ltda Cnpj</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -603,10 +603,8 @@
           <t>(28) 2749-5500</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>552827495500</t>
-        </is>
+      <c r="I3" t="n">
+        <v>552827495500</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -643,7 +641,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CNPJ: 58.524.532/0001-08</t>
+          <t>Cnpj: 58.524.532/0001-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -681,10 +679,8 @@
           <t>(02) 5581-5700</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>550255815700</t>
-        </is>
+      <c r="I4" t="n">
+        <v>550255815700</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -759,10 +755,8 @@
           <t>(41) 3253-1907</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>554132531907</t>
-        </is>
+      <c r="I5" t="n">
+        <v>554132531907</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -837,10 +831,8 @@
           <t>(41) 9876-2903</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>554198762903</t>
-        </is>
+      <c r="I6" t="n">
+        <v>554198762903</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -877,7 +869,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dra.Keslen_Geffer</t>
+          <t>Dra.keslen_geffer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -915,10 +907,8 @@
           <t>(41) 3252-1119</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>554132521119</t>
-        </is>
+      <c r="I7" t="n">
+        <v>554132521119</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -955,7 +945,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Encontrar seu smartphone</t>
+          <t>Encontrar Seu Smartphone</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1029,7 +1019,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>Link To Instagram.com</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1103,7 +1093,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Clnica Felpe Odontologia Curitiba</t>
+          <t>Clnica Felpe Odontologia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1141,10 +1131,8 @@
           <t>41997321</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5541997321</t>
-        </is>
+      <c r="I10" t="n">
+        <v>5541997321</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1181,7 +1169,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UpClin Odontologia Curitiba</t>
+          <t>Upclin Odontologia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,7 +1243,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SV Odontologia • Tratamento Invisalign e Orto</t>
+          <t>Sv Odontologia • Tratamento Invisalign e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1367,10 +1355,8 @@
           <t>(41) 3342-2121</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>554133422121</t>
-        </is>
+      <c r="I13" t="n">
+        <v>554133422121</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1407,7 +1393,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dental Esthetic Center / odontologia curitiba</t>
+          <t>Dental Esthetic Center</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1445,10 +1431,8 @@
           <t>(41) 99280-3875</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5541992803875</t>
-        </is>
+      <c r="I14" t="n">
+        <v>5541992803875</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1485,7 +1469,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Odonto Pio XII</t>
+          <t>Odonto Pio Xii</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1597,10 +1581,8 @@
           <t>(41) 98868-8164</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5541988688164</t>
-        </is>
+      <c r="I16" t="n">
+        <v>5541988688164</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1675,10 +1657,8 @@
           <t>(41) 98444-8862</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5541984448862</t>
-        </is>
+      <c r="I17" t="n">
+        <v>5541984448862</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1715,7 +1695,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ODONTOLOGIA COSTA</t>
+          <t>Odontologia Costa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1753,10 +1733,8 @@
           <t>(41) 3322-9504</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>554133229504</t>
-        </is>
+      <c r="I18" t="n">
+        <v>554133229504</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1831,10 +1809,8 @@
           <t>(41) 98825-8833</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5541988258833</t>
-        </is>
+      <c r="I19" t="n">
+        <v>5541988258833</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1909,10 +1885,8 @@
           <t>(41) 99257-8253</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5541992578253</t>
-        </is>
+      <c r="I20" t="n">
+        <v>5541992578253</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1949,7 +1923,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Consultrio odontolgico</t>
+          <t>Consultrio Odontolgico</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1987,10 +1961,8 @@
           <t>(19) 4108-2486</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>551941082486</t>
-        </is>
+      <c r="I21" t="n">
+        <v>551941082486</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2101,7 +2073,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Link To Facebook.com</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2213,10 +2185,8 @@
           <t>(34) 3411-4813</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>553434114813</t>
-        </is>
+      <c r="I24" t="n">
+        <v>553434114813</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2401,7 +2371,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10 melhores dentistas para Curitiba</t>
+          <t>10 Melhores Dentistas para</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2513,10 +2483,8 @@
           <t>(41) 99567-6216</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5541995676216</t>
-        </is>
+      <c r="I28" t="n">
+        <v>5541995676216</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2553,7 +2521,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Clnica odontolgica de Curitiba</t>
+          <t>Clnica Odontolgica de</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2591,10 +2559,8 @@
           <t>(41) 4101-3337</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>554141013337</t>
-        </is>
+      <c r="I29" t="n">
+        <v>554141013337</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2631,7 +2597,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10 MELHORES Clnicas Odontolgicas</t>
+          <t>10 Melhores Clnicas Odontolgicas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2705,7 +2671,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Maxiclin Odontologia Curitiba</t>
+          <t>Maxiclin Odontologia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2743,10 +2709,8 @@
           <t>(41) 98519-4512</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5541985194512</t>
-        </is>
+      <c r="I31" t="n">
+        <v>5541985194512</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2821,10 +2785,8 @@
           <t>(41) 3257-1026</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>554132571026</t>
-        </is>
+      <c r="I32" t="n">
+        <v>554132571026</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2973,10 +2935,8 @@
           <t>(19) 3816-7455</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>551938167455</t>
-        </is>
+      <c r="I34" t="n">
+        <v>551938167455</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3051,10 +3011,8 @@
           <t>(41) 3408-5222</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>554134085222</t>
-        </is>
+      <c r="I35" t="n">
+        <v>554134085222</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3203,10 +3161,8 @@
           <t>(47) 1562-3100</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>554715623100</t>
-        </is>
+      <c r="I37" t="n">
+        <v>554715623100</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3281,10 +3237,8 @@
           <t>(41) 3264-1984</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>554132641984</t>
-        </is>
+      <c r="I38" t="n">
+        <v>554132641984</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3359,10 +3313,8 @@
           <t>(41) 3022-2999</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>554130222999</t>
-        </is>
+      <c r="I39" t="n">
+        <v>554130222999</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3399,7 +3351,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dentista Ortodontista Invisalign Curitiba</t>
+          <t>Dentista Ortodontista Invisalign</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3511,10 +3463,8 @@
           <t>(41) 99595-1636</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5541995951636</t>
-        </is>
+      <c r="I41" t="n">
+        <v>5541995951636</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3589,10 +3539,8 @@
           <t>(41) 99861-8127</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5541998618127</t>
-        </is>
+      <c r="I42" t="n">
+        <v>5541998618127</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3629,7 +3577,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Os melhores barbeiros perto de mim</t>
+          <t>Os Melhores Barbeiros Perto de Mim</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3667,10 +3615,8 @@
           <t>34028872</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5534028872</t>
-        </is>
+      <c r="I43" t="n">
+        <v>5534028872</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3745,10 +3691,8 @@
           <t>(41) 99894-4124</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5541998944124</t>
-        </is>
+      <c r="I44" t="n">
+        <v>5541998944124</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3785,7 +3729,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15 Melhores Barbearias no Rebouas</t>
+          <t>15 Melhores Barbearias No Rebouas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3859,7 +3803,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>barbearias</t>
+          <t>Barbearias</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3971,10 +3915,8 @@
           <t>(41) 3598-9540</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>554135989540</t>
-        </is>
+      <c r="I47" t="n">
+        <v>554135989540</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -4049,10 +3991,8 @@
           <t>(41) 99894-4124</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5541998944124</t>
-        </is>
+      <c r="I48" t="n">
+        <v>5541998944124</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -4127,10 +4067,8 @@
           <t>(41) 3014-9413</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>554130149413</t>
-        </is>
+      <c r="I49" t="n">
+        <v>554130149413</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -4167,7 +4105,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AutoRank para Barbearias</t>
+          <t>Autorank para Barbearias</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4217,8 @@
           <t>(41) 98475-3472</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5541984753472</t>
-        </is>
+      <c r="I51" t="n">
+        <v>5541984753472</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -4357,10 +4293,8 @@
           <t>(41) 1111-1111</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>554111111111</t>
-        </is>
+      <c r="I52" t="n">
+        <v>554111111111</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4397,7 +4331,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CNPJ 53.441.822/0001-74</t>
+          <t>Cnpj 53.441.822/0001-74</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
